--- a/src/app/modules/dashboard/excel_files/seafood-recipes-oil-free-complete.xlsx
+++ b/src/app/modules/dashboard/excel_files/seafood-recipes-oil-free-complete.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V57"/>
+  <dimension ref="A1:W57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -446,95 +446,100 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
+          <t>recipe_id</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
           <t>ingredients</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>instructions</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>nutritional</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>serving_size</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>prep_time</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>oils</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>whole_food_type</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>flavor</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>weight_and_muscle</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>kid_approved</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>no_weekend_prep</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>holiday_recipes</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>serving_temperature</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>ratting</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>recipe_tips</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>prep</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="V1" s="1" t="inlineStr">
         <is>
           <t>prep_time_note</t>
         </is>
       </c>
-      <c r="V1" s="1" t="inlineStr">
+      <c r="W1" s="1" t="inlineStr">
         <is>
           <t>prep_list</t>
         </is>
@@ -558,10 +563,15 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>4490</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '8 corn tortillas', '1/2 teaspoon cumin', '1/2 teaspoon smoked paprika', '1 teaspoon lime juice', '1/2 teaspoon salt', '1/2 cup shredded cabbage', '1/4 cup chopped cilantro']</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="F2" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Add shrimp, cumin, paprika, lime juice, and salt. Cook for 5 minutes, stirring occasionally.
@@ -570,59 +580,59 @@
 5. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>{"calories": 290, "protein": 36, "carbs": 38, "fiber": 6, "fat": 2}</t>
         </is>
       </c>
-      <c r="G2" t="n">
+      <c r="H2" t="n">
         <v>4</v>
       </c>
-      <c r="H2" t="n">
+      <c r="I2" t="n">
         <v>15</v>
       </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J2" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="L2" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="M2" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="N2" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N2" t="b">
-        <v>0</v>
-      </c>
       <c r="O2" t="b">
         <v>0</v>
       </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr">
+      <c r="P2" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R2" t="n">
-        <v>0</v>
-      </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
+      <c r="S2" t="n">
+        <v>0</v>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Add shrimp, cumin, paprika, lime juice, and salt. Cook for 5 minutes, stirring occasionally.
@@ -631,8 +641,8 @@
 5. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr">
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr">
         <is>
           <t>['Heat a non-stick pan over medium heat.', 'Add shrimp, cumin, paprika, lime juice, and salt. Cook for 5 minutes, stirring occasionally.', 'Warm tortillas in a dry skillet.', 'Fill tortillas with shrimp, cabbage, and cilantro.', 'Cook time: 5 MINS']</t>
         </is>
@@ -656,10 +666,15 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
+          <t>4491</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
           <t>['4 cod fillets (low-mercury)', '1 teaspoon lemon juice', '2 cloves garlic, minced', '1/2 teaspoon salt', '1 teaspoon dried parsley']</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="F3" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place cod fillets on a parchment-lined baking sheet.
@@ -668,59 +683,59 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
+      <c r="G3" t="inlineStr">
         <is>
           <t>{"calories": 200, "protein": 40, "carbs": 2, "fiber": 0, "fat": 1}</t>
         </is>
       </c>
-      <c r="G3" t="n">
+      <c r="H3" t="n">
         <v>4</v>
       </c>
-      <c r="H3" t="n">
+      <c r="I3" t="n">
         <v>20</v>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="L3" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N3" t="b">
-        <v>0</v>
-      </c>
       <c r="O3" t="b">
         <v>0</v>
       </c>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr">
+      <c r="P3" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R3" t="n">
-        <v>0</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
+      <c r="S3" t="n">
+        <v>0</v>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place cod fillets on a parchment-lined baking sheet.
@@ -729,8 +744,8 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr">
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place cod fillets on a parchment-lined baking sheet.', 'Rub with lemon juice, garlic, salt, and parsley.', 'Bake for 15 minutes until flaky.', 'Cook time: 15 MINS']</t>
         </is>
@@ -754,77 +769,82 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
+          <t>4492</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, cooked and peeled', '1 cup diced mango', '1/2 cup diced cucumber', '1/4 cup diced red onion', '1 teaspoon lime juice', '1/2 teaspoon chili powder', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="F4" t="inlineStr">
         <is>
           <t>1. Combine shrimp, mango, cucumber, red onion, lime juice, chili powder, and salt in a bowl.
 2. Toss well and serve chilled.
 3. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="G4" t="inlineStr">
         <is>
           <t>{"calories": 280, "protein": 35, "carbs": 18, "fiber": 3, "fat": 1}</t>
         </is>
       </c>
-      <c r="G4" t="n">
+      <c r="H4" t="n">
         <v>4</v>
       </c>
-      <c r="H4" t="n">
+      <c r="I4" t="n">
         <v>10</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J4" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N4" t="b">
-        <v>0</v>
-      </c>
       <c r="O4" t="b">
         <v>0</v>
       </c>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="inlineStr">
+      <c r="P4" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr">
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr">
         <is>
           <t>1. Combine shrimp, mango, cucumber, red onion, lime juice, chili powder, and salt in a bowl.
 2. Toss well and serve chilled.
 3. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr">
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr">
         <is>
           <t>['Combine shrimp, mango, cucumber, red onion, lime juice, chili powder, and salt in a bowl.', 'Toss well and serve chilled.', 'Cook time: 10 MINS']</t>
         </is>
@@ -843,15 +863,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Oil-Free Baked Tilapia with Garlic &amp; Herbs</t>
+          <t>Oil-Free Baked Tilapia With Garlic &amp; Herbs</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
+          <t>4493</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
           <t>['4 tilapia fillets', '2 cloves garlic, minced', '1 teaspoon lemon juice', '1/2 teaspoon oregano', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E5" t="inlineStr">
+      <c r="F5" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place tilapia on a parchment-lined baking sheet.
@@ -860,59 +885,59 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F5" t="inlineStr">
+      <c r="G5" t="inlineStr">
         <is>
           <t>{"calories": 220, "protein": 45, "carbs": 2, "fiber": 0, "fat": 1}</t>
         </is>
       </c>
-      <c r="G5" t="n">
+      <c r="H5" t="n">
         <v>4</v>
       </c>
-      <c r="H5" t="n">
+      <c r="I5" t="n">
         <v>20</v>
       </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J5" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N5" t="b">
-        <v>0</v>
-      </c>
       <c r="O5" t="b">
         <v>0</v>
       </c>
-      <c r="P5" t="inlineStr"/>
-      <c r="Q5" t="inlineStr">
+      <c r="P5" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R5" t="n">
-        <v>0</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr">
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place tilapia on a parchment-lined baking sheet.
@@ -921,8 +946,8 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr">
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place tilapia on a parchment-lined baking sheet.', 'Rub with garlic, lemon juice, oregano, and salt.', 'Bake for 15 minutes until flaky.', 'Cook time: 15 MINS']</t>
         </is>
@@ -946,10 +971,15 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
+          <t>4494</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
           <t>['4 salmon fillets', '1 teaspoon lime juice', '2 cloves garlic, minced', '1 teaspoon dried parsley', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E6" t="inlineStr">
+      <c r="F6" t="inlineStr">
         <is>
           <t>1. Preheat a grill pan over medium heat.
 2. Rub salmon fillets with lime juice, garlic, parsley, and salt.
@@ -957,59 +987,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F6" t="inlineStr">
+      <c r="G6" t="inlineStr">
         <is>
           <t>{"calories": 300, "protein": 40, "carbs": 1, "fiber": 0, "fat": 12}</t>
         </is>
       </c>
-      <c r="G6" t="n">
+      <c r="H6" t="n">
         <v>4</v>
       </c>
-      <c r="H6" t="n">
+      <c r="I6" t="n">
         <v>15</v>
       </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J6" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="L6" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M6" t="inlineStr">
+      <c r="N6" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N6" t="b">
-        <v>0</v>
-      </c>
       <c r="O6" t="b">
         <v>0</v>
       </c>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr">
+      <c r="P6" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr">
         <is>
           <t>1. Preheat a grill pan over medium heat.
 2. Rub salmon fillets with lime juice, garlic, parsley, and salt.
@@ -1017,8 +1047,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr">
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr">
         <is>
           <t>['Preheat a grill pan over medium heat.', 'Rub salmon fillets with lime juice, garlic, parsley, and salt.', 'Grill for 4 minutes per side or until fully cooked.', 'Cook time: 5 MINS']</t>
         </is>
@@ -1042,77 +1072,82 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
+          <t>4495</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, cooked and peeled', '1 avocado, diced', '1/4 cup diced red onion', '1 teaspoon lime juice', '1/2 teaspoon salt', '8 large lettuce leaves']</t>
         </is>
       </c>
-      <c r="E7" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>1. Mix shrimp, avocado, red onion, lime juice, and salt in a bowl.
 2. Scoop into lettuce leaves and serve.
 3. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="F7" t="inlineStr">
+      <c r="G7" t="inlineStr">
         <is>
           <t>{"calories": 280, "protein": 35, "carbs": 8, "fiber": 4, "fat": 10}</t>
         </is>
       </c>
-      <c r="G7" t="n">
+      <c r="H7" t="n">
         <v>4</v>
       </c>
-      <c r="H7" t="n">
+      <c r="I7" t="n">
         <v>10</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J7" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss', 'wraps']</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="L7" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N7" t="b">
-        <v>0</v>
-      </c>
       <c r="O7" t="b">
         <v>0</v>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr">
+      <c r="P7" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr">
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr">
         <is>
           <t>1. Mix shrimp, avocado, red onion, lime juice, and salt in a bowl.
 2. Scoop into lettuce leaves and serve.
 3. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr">
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr">
         <is>
           <t>['Mix shrimp, avocado, red onion, lime juice, and salt in a bowl.', 'Scoop into lettuce leaves and serve.', 'Cook time: 10 MINS']</t>
         </is>
@@ -1136,10 +1171,15 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
+          <t>4496</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
           <t>['1 pound scallops', '1 teaspoon lemon juice', '1 teaspoon dried basil', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E8" t="inlineStr">
+      <c r="F8" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Add scallops, lemon juice, basil, and salt.
@@ -1147,59 +1187,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F8" t="inlineStr">
+      <c r="G8" t="inlineStr">
         <is>
           <t>{"calories": 250, "protein": 42, "carbs": 2, "fiber": 0, "fat": 1}</t>
         </is>
       </c>
-      <c r="G8" t="n">
+      <c r="H8" t="n">
         <v>4</v>
       </c>
-      <c r="H8" t="n">
+      <c r="I8" t="n">
         <v>10</v>
       </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J8" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N8" t="b">
-        <v>0</v>
-      </c>
       <c r="O8" t="b">
         <v>0</v>
       </c>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="inlineStr">
+      <c r="P8" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R8" t="n">
-        <v>0</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr">
+      <c r="S8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Add scallops, lemon juice, basil, and salt.
@@ -1207,8 +1247,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr">
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr">
         <is>
           <t>['Heat a non-stick pan over medium heat.', 'Add scallops, lemon juice, basil, and salt.', 'Cook for 2 minutes per side until golden.', 'Cook time: 5 MINS']</t>
         </is>
@@ -1232,10 +1272,15 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
+          <t>4497</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
           <t>['4 cod fillets', '2 cloves garlic, minced', '1 teaspoon lemon juice', '1 teaspoon parsley', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E9" t="inlineStr">
+      <c r="F9" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place cod fillets on parchment paper.
@@ -1244,59 +1289,59 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F9" t="inlineStr">
+      <c r="G9" t="inlineStr">
         <is>
           <t>{"calories": 200, "protein": 40, "carbs": 2, "fiber": 0, "fat": 1}</t>
         </is>
       </c>
-      <c r="G9" t="n">
+      <c r="H9" t="n">
         <v>4</v>
       </c>
-      <c r="H9" t="n">
+      <c r="I9" t="n">
         <v>20</v>
       </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J9" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K9" t="inlineStr">
+      <c r="L9" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L9" t="inlineStr">
+      <c r="M9" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M9" t="inlineStr">
+      <c r="N9" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N9" t="b">
-        <v>0</v>
-      </c>
       <c r="O9" t="b">
         <v>0</v>
       </c>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr">
+      <c r="P9" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R9" t="n">
-        <v>0</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr">
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place cod fillets on parchment paper.
@@ -1305,8 +1350,8 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr">
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place cod fillets on parchment paper.', 'Rub with garlic, lemon juice, parsley, and salt.', 'Bake for 15 minutes until flaky.', 'Cook time: 15 MINS']</t>
         </is>
@@ -1330,10 +1375,15 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
+          <t>4498</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
           <t>['4 tilapia fillets', '1 teaspoon lime juice', '1 teaspoon chili powder', '1/2 teaspoon garlic powder', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="F10" t="inlineStr">
         <is>
           <t>1. Preheat a grill pan over medium heat.
 2. Coat tilapia fillets with lime juice, chili powder, garlic powder, and salt.
@@ -1341,59 +1391,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F10" t="inlineStr">
+      <c r="G10" t="inlineStr">
         <is>
           <t>{"calories": 220, "protein": 45, "carbs": 1, "fiber": 0, "fat": 2}</t>
         </is>
       </c>
-      <c r="G10" t="n">
+      <c r="H10" t="n">
         <v>4</v>
       </c>
-      <c r="H10" t="n">
+      <c r="I10" t="n">
         <v>15</v>
       </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K10" t="inlineStr">
+      <c r="L10" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N10" t="b">
-        <v>0</v>
-      </c>
       <c r="O10" t="b">
         <v>0</v>
       </c>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="inlineStr">
+      <c r="P10" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr">
+      <c r="S10" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr">
         <is>
           <t>1. Preheat a grill pan over medium heat.
 2. Coat tilapia fillets with lime juice, chili powder, garlic powder, and salt.
@@ -1401,8 +1451,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr">
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr">
         <is>
           <t>['Preheat a grill pan over medium heat.', 'Coat tilapia fillets with lime juice, chili powder, garlic powder, and salt.', 'Grill for 4 minutes per side until flaky.', 'Cook time: 5 MINS']</t>
         </is>
@@ -1426,10 +1476,15 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
+          <t>4499</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '1 teaspoon lime juice', '2 cloves garlic, minced', '1 teaspoon dried oregano', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E11" t="inlineStr">
+      <c r="F11" t="inlineStr">
         <is>
           <t>1. Thread shrimp onto skewers.
 2. Rub with lime juice, garlic, oregano, and salt.
@@ -1437,59 +1492,59 @@
 4. Cook time: 3 MINS</t>
         </is>
       </c>
-      <c r="F11" t="inlineStr">
+      <c r="G11" t="inlineStr">
         <is>
           <t>{"calories": 250, "protein": 38, "carbs": 3, "fiber": 0, "fat": 2}</t>
         </is>
       </c>
-      <c r="G11" t="n">
+      <c r="H11" t="n">
         <v>4</v>
       </c>
-      <c r="H11" t="n">
+      <c r="I11" t="n">
         <v>15</v>
       </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J11" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K11" t="inlineStr">
+      <c r="L11" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
+      <c r="M11" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M11" t="inlineStr">
+      <c r="N11" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N11" t="b">
-        <v>0</v>
-      </c>
       <c r="O11" t="b">
         <v>0</v>
       </c>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="inlineStr">
+      <c r="P11" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr">
+      <c r="S11" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr">
         <is>
           <t>1. Thread shrimp onto skewers.
 2. Rub with lime juice, garlic, oregano, and salt.
@@ -1497,8 +1552,8 @@
 4. Cook time: 3 MINS</t>
         </is>
       </c>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr">
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr">
         <is>
           <t>['Thread shrimp onto skewers.', 'Rub with lime juice, garlic, oregano, and salt.', 'Grill for 3 minutes per side until fully cooked.', 'Cook time: 3 MINS']</t>
         </is>
@@ -1522,10 +1577,15 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
+          <t>4500</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
           <t>['4 salmon fillets', '1 teaspoon lime juice', '2 cloves garlic, minced', '1 teaspoon chopped cilantro', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E12" t="inlineStr">
+      <c r="F12" t="inlineStr">
         <is>
           <t>1. Preheat a grill pan over medium heat.
 2. Rub salmon with lime juice, garlic, cilantro, and salt.
@@ -1533,59 +1593,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F12" t="inlineStr">
+      <c r="G12" t="inlineStr">
         <is>
           <t>{"calories": 300, "protein": 40, "carbs": 1, "fiber": 0, "fat": 12}</t>
         </is>
       </c>
-      <c r="G12" t="n">
+      <c r="H12" t="n">
         <v>4</v>
       </c>
-      <c r="H12" t="n">
+      <c r="I12" t="n">
         <v>15</v>
       </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J12" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K12" t="inlineStr">
+      <c r="L12" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L12" t="inlineStr">
+      <c r="M12" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M12" t="inlineStr">
+      <c r="N12" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N12" t="b">
-        <v>0</v>
-      </c>
       <c r="O12" t="b">
         <v>0</v>
       </c>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="inlineStr">
+      <c r="P12" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr">
+      <c r="S12" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr">
         <is>
           <t>1. Preheat a grill pan over medium heat.
 2. Rub salmon with lime juice, garlic, cilantro, and salt.
@@ -1593,8 +1653,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr">
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr">
         <is>
           <t>['Preheat a grill pan over medium heat.', 'Rub salmon with lime juice, garlic, cilantro, and salt.', 'Grill for 4 minutes per side until fully cooked.', 'Cook time: 5 MINS']</t>
         </is>
@@ -1618,10 +1678,15 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
+          <t>4501</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '8 corn tortillas', '1/2 teaspoon cumin', '1/2 teaspoon chili powder', '1 teaspoon lime juice', '1/2 teaspoon salt', '1/2 cup shredded cabbage']</t>
         </is>
       </c>
-      <c r="E13" t="inlineStr">
+      <c r="F13" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Add shrimp, cumin, chili powder, lime juice, and salt. Cook for 5 minutes, stirring occasionally.
@@ -1629,59 +1694,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F13" t="inlineStr">
+      <c r="G13" t="inlineStr">
         <is>
           <t>{"calories": 290, "protein": 36, "carbs": 38, "fiber": 6, "fat": 2}</t>
         </is>
       </c>
-      <c r="G13" t="n">
+      <c r="H13" t="n">
         <v>4</v>
       </c>
-      <c r="H13" t="n">
+      <c r="I13" t="n">
         <v>15</v>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K13" t="inlineStr">
+      <c r="L13" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M13" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N13" t="b">
-        <v>0</v>
-      </c>
       <c r="O13" t="b">
         <v>0</v>
       </c>
-      <c r="P13" t="inlineStr"/>
-      <c r="Q13" t="inlineStr">
+      <c r="P13" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R13" t="n">
-        <v>0</v>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr">
+      <c r="S13" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Add shrimp, cumin, chili powder, lime juice, and salt. Cook for 5 minutes, stirring occasionally.
@@ -1689,8 +1754,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr">
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr">
         <is>
           <t>['Heat a non-stick pan over medium heat.', 'Add shrimp, cumin, chili powder, lime juice, and salt. Cook for 5 minutes, stirring occasionally.', 'Warm tortillas and fill with shrimp and cabbage.', 'Cook time: 5 MINS']</t>
         </is>
@@ -1714,77 +1779,82 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
+          <t>4502</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, cooked and peeled', '1/2 teaspoon chipotle powder', '1 teaspoon lime juice', '1/2 teaspoon salt', '1 cup chopped romaine lettuce']</t>
         </is>
       </c>
-      <c r="E14" t="inlineStr">
+      <c r="F14" t="inlineStr">
         <is>
           <t>1. Mix shrimp with chipotle powder, lime juice, and salt.
 2. Serve over chopped romaine.
 3. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="F14" t="inlineStr">
+      <c r="G14" t="inlineStr">
         <is>
           <t>{"calories": 260, "protein": 35, "carbs": 8, "fiber": 2, "fat": 2}</t>
         </is>
       </c>
-      <c r="G14" t="n">
+      <c r="H14" t="n">
         <v>4</v>
       </c>
-      <c r="H14" t="n">
+      <c r="I14" t="n">
         <v>10</v>
       </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J14" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K14" t="inlineStr">
+      <c r="L14" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M14" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N14" t="b">
-        <v>0</v>
-      </c>
       <c r="O14" t="b">
         <v>0</v>
       </c>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="inlineStr">
+      <c r="P14" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R14" t="n">
-        <v>0</v>
-      </c>
-      <c r="S14" t="inlineStr"/>
-      <c r="T14" t="inlineStr">
+      <c r="S14" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr">
         <is>
           <t>1. Mix shrimp with chipotle powder, lime juice, and salt.
 2. Serve over chopped romaine.
 3. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="U14" t="inlineStr"/>
-      <c r="V14" t="inlineStr">
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr">
         <is>
           <t>['Mix shrimp with chipotle powder, lime juice, and salt.', 'Serve over chopped romaine.', 'Cook time: 10 MINS']</t>
         </is>
@@ -1808,10 +1878,15 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
+          <t>4503</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '1 teaspoon lemon juice', '2 cloves garlic, minced', '1 teaspoon dried basil', '1/2 teaspoon salt', '1 cup broccoli florets']</t>
         </is>
       </c>
-      <c r="E15" t="inlineStr">
+      <c r="F15" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Add shrimp, lemon juice, garlic, basil, and salt.
@@ -1819,59 +1894,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F15" t="inlineStr">
+      <c r="G15" t="inlineStr">
         <is>
           <t>{"calories": 260, "protein": 38, "carbs": 8, "fiber": 2, "fat": 2}</t>
         </is>
       </c>
-      <c r="G15" t="n">
+      <c r="H15" t="n">
         <v>4</v>
       </c>
-      <c r="H15" t="n">
+      <c r="I15" t="n">
         <v>15</v>
       </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J15" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K15" t="inlineStr">
+      <c r="L15" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L15" t="inlineStr">
+      <c r="M15" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M15" t="inlineStr">
+      <c r="N15" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N15" t="b">
-        <v>0</v>
-      </c>
       <c r="O15" t="b">
         <v>0</v>
       </c>
-      <c r="P15" t="inlineStr"/>
-      <c r="Q15" t="inlineStr">
+      <c r="P15" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="inlineStr"/>
-      <c r="T15" t="inlineStr">
+      <c r="S15" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Add shrimp, lemon juice, garlic, basil, and salt.
@@ -1879,8 +1954,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U15" t="inlineStr"/>
-      <c r="V15" t="inlineStr">
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr">
         <is>
           <t>['Heat a non-stick pan over medium heat.', 'Add shrimp, lemon juice, garlic, basil, and salt.', 'Stir in broccoli and cook for 5 minutes.', 'Cook time: 5 MINS']</t>
         </is>
@@ -1904,10 +1979,15 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
+          <t>4504</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
           <t>['2 cans sardines (low-mercury, packed in water)', '1/2 cup diced tomatoes', '1/4 cup diced cucumber', '1 teaspoon lime juice', '1/2 teaspoon smoked paprika', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E16" t="inlineStr">
+      <c r="F16" t="inlineStr">
         <is>
           <t>1. Drain sardines and mash in a bowl.
 2. Mix with tomatoes, cucumber, lime juice, paprika, and salt.
@@ -1915,59 +1995,59 @@
 4. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="F16" t="inlineStr">
+      <c r="G16" t="inlineStr">
         <is>
           <t>{"calories": 250, "protein": 32, "carbs": 6, "fiber": 2, "fat": 8}</t>
         </is>
       </c>
-      <c r="G16" t="n">
+      <c r="H16" t="n">
         <v>4</v>
       </c>
-      <c r="H16" t="n">
+      <c r="I16" t="n">
         <v>10</v>
       </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K16" t="inlineStr">
+      <c r="L16" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N16" t="b">
-        <v>0</v>
-      </c>
       <c r="O16" t="b">
         <v>0</v>
       </c>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="inlineStr">
+      <c r="P16" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="inlineStr"/>
-      <c r="T16" t="inlineStr">
+      <c r="S16" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr">
         <is>
           <t>1. Drain sardines and mash in a bowl.
 2. Mix with tomatoes, cucumber, lime juice, paprika, and salt.
@@ -1975,8 +2055,8 @@
 4. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="U16" t="inlineStr"/>
-      <c r="V16" t="inlineStr">
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr">
         <is>
           <t>['Drain sardines and mash in a bowl.', 'Mix with tomatoes, cucumber, lime juice, paprika, and salt.', 'Serve chilled or at room temperature.', 'Cook time: 10 MINS']</t>
         </is>
@@ -2000,10 +2080,15 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
+          <t>4505</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '8 oz whole wheat pasta', '2 cloves garlic, minced', '1 teaspoon lemon juice', '1 teaspoon chopped parsley', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E17" t="inlineStr">
+      <c r="F17" t="inlineStr">
         <is>
           <t>1. Cook pasta according to package instructions.
 2. In a non-stick pan, cook shrimp with garlic, lemon juice, parsley, and salt for 5 minutes.
@@ -2011,59 +2096,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="G17" t="inlineStr">
         <is>
           <t>{"calories": 380, "protein": 42, "carbs": 50, "fiber": 7, "fat": 3}</t>
         </is>
       </c>
-      <c r="G17" t="n">
+      <c r="H17" t="n">
         <v>4</v>
       </c>
-      <c r="H17" t="n">
+      <c r="I17" t="n">
         <v>20</v>
       </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J17" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'pasta', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K17" t="inlineStr">
+      <c r="L17" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
+      <c r="M17" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M17" t="inlineStr">
+      <c r="N17" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N17" t="b">
-        <v>0</v>
-      </c>
       <c r="O17" t="b">
         <v>0</v>
       </c>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="inlineStr">
+      <c r="P17" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="inlineStr"/>
-      <c r="T17" t="inlineStr">
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr">
         <is>
           <t>1. Cook pasta according to package instructions.
 2. In a non-stick pan, cook shrimp with garlic, lemon juice, parsley, and salt for 5 minutes.
@@ -2071,8 +2156,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U17" t="inlineStr"/>
-      <c r="V17" t="inlineStr">
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr">
         <is>
           <t>['Cook pasta according to package instructions.', 'In a non-stick pan, cook shrimp with garlic, lemon juice, parsley, and salt for 5 minutes.', 'Toss shrimp with cooked pasta and serve.', 'Cook time: 5 MINS']</t>
         </is>
@@ -2096,10 +2181,15 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
+          <t>4506</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '4 cups vegetable broth', '1/2 cup diced tomatoes', '1/2 cup diced onions', '1 teaspoon cumin', '1 teaspoon smoked paprika', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E18" t="inlineStr">
+      <c r="F18" t="inlineStr">
         <is>
           <t>1. Bring broth to a boil.
 2. Add shrimp, tomatoes, onions, cumin, paprika, and salt.
@@ -2107,59 +2197,59 @@
 4. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="F18" t="inlineStr">
+      <c r="G18" t="inlineStr">
         <is>
           <t>{"calories": 260, "protein": 40, "carbs": 10, "fiber": 2, "fat": 2}</t>
         </is>
       </c>
-      <c r="G18" t="n">
+      <c r="H18" t="n">
         <v>4</v>
       </c>
-      <c r="H18" t="n">
+      <c r="I18" t="n">
         <v>20</v>
       </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'soups', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K18" t="inlineStr">
+      <c r="L18" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M18" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N18" t="b">
-        <v>0</v>
-      </c>
       <c r="O18" t="b">
         <v>0</v>
       </c>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="inlineStr">
+      <c r="P18" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R18" t="n">
-        <v>0</v>
-      </c>
-      <c r="S18" t="inlineStr"/>
-      <c r="T18" t="inlineStr">
+      <c r="S18" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr">
         <is>
           <t>1. Bring broth to a boil.
 2. Add shrimp, tomatoes, onions, cumin, paprika, and salt.
@@ -2167,8 +2257,8 @@
 4. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="U18" t="inlineStr"/>
-      <c r="V18" t="inlineStr">
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr">
         <is>
           <t>['Bring broth to a boil.', 'Add shrimp, tomatoes, onions, cumin, paprika, and salt.', 'Simmer for 10 minutes and serve warm.', 'Cook time: 10 MINS']</t>
         </is>
@@ -2187,15 +2277,20 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Oil-Free Grilled Salmon with Mango Salsa</t>
+          <t>Oil-Free Grilled Salmon With Mango Salsa</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
+          <t>4507</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
           <t>['4 salmon fillets', '1 teaspoon lime juice', '1 cup diced mango', '1/4 cup diced red onion', '1 teaspoon chopped cilantro', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E19" t="inlineStr">
+      <c r="F19" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan over medium heat.
 2. Rub salmon with lime juice and salt. Grill for 4 minutes per side.
@@ -2203,59 +2298,59 @@
 4. Cook time: 4 MINS</t>
         </is>
       </c>
-      <c r="F19" t="inlineStr">
+      <c r="G19" t="inlineStr">
         <is>
           <t>{"calories": 320, "protein": 42, "carbs": 12, "fiber": 3, "fat": 10}</t>
         </is>
       </c>
-      <c r="G19" t="n">
+      <c r="H19" t="n">
         <v>4</v>
       </c>
-      <c r="H19" t="n">
+      <c r="I19" t="n">
         <v>20</v>
       </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J19" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K19" t="inlineStr">
+      <c r="L19" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="M19" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M19" t="inlineStr">
+      <c r="N19" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N19" t="b">
-        <v>0</v>
-      </c>
       <c r="O19" t="b">
         <v>0</v>
       </c>
-      <c r="P19" t="inlineStr"/>
-      <c r="Q19" t="inlineStr">
+      <c r="P19" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="inlineStr"/>
-      <c r="T19" t="inlineStr">
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan over medium heat.
 2. Rub salmon with lime juice and salt. Grill for 4 minutes per side.
@@ -2263,8 +2358,8 @@
 4. Cook time: 4 MINS</t>
         </is>
       </c>
-      <c r="U19" t="inlineStr"/>
-      <c r="V19" t="inlineStr">
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr">
         <is>
           <t>['Preheat grill or grill pan over medium heat.', 'Rub salmon with lime juice and salt. Grill for 4 minutes per side.', 'Mix mango, red onion, and cilantro for salsa. Serve over salmon.', 'Cook time: 4 MINS']</t>
         </is>
@@ -2288,10 +2383,15 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
+          <t>4508</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
           <t>['4 trout fillets', '1 teaspoon lemon juice', '1 teaspoon dried oregano', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E20" t="inlineStr">
+      <c r="F20" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place trout fillets on parchment paper.
@@ -2300,59 +2400,59 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F20" t="inlineStr">
+      <c r="G20" t="inlineStr">
         <is>
           <t>{"calories": 290, "protein": 40, "carbs": 1, "fiber": 0, "fat": 10}</t>
         </is>
       </c>
-      <c r="G20" t="n">
+      <c r="H20" t="n">
         <v>4</v>
       </c>
-      <c r="H20" t="n">
+      <c r="I20" t="n">
         <v>20</v>
       </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J20" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K20" t="inlineStr">
+      <c r="L20" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L20" t="inlineStr">
+      <c r="M20" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M20" t="inlineStr">
+      <c r="N20" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N20" t="b">
-        <v>0</v>
-      </c>
       <c r="O20" t="b">
         <v>0</v>
       </c>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="inlineStr">
+      <c r="P20" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q20" t="inlineStr"/>
+      <c r="R20" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R20" t="n">
-        <v>0</v>
-      </c>
-      <c r="S20" t="inlineStr"/>
-      <c r="T20" t="inlineStr">
+      <c r="S20" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" t="inlineStr"/>
+      <c r="U20" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place trout fillets on parchment paper.
@@ -2361,8 +2461,8 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr"/>
-      <c r="V20" t="inlineStr">
+      <c r="V20" t="inlineStr"/>
+      <c r="W20" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place trout fillets on parchment paper.', 'Rub with lemon juice, oregano, and salt.', 'Bake for 15 minutes until flaky.', 'Cook time: 15 MINS']</t>
         </is>
@@ -2386,77 +2486,82 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
+          <t>4509</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '1 cup cooked quinoa', '1 teaspoon lime juice', '1 teaspoon chopped cilantro', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E21" t="inlineStr">
+      <c r="F21" t="inlineStr">
         <is>
           <t>1. Cook shrimp in a non-stick pan for 5 minutes with lime juice, cilantro, and salt.
 2. Serve over cooked quinoa.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="G21" t="inlineStr">
         <is>
           <t>{"calories": 320, "protein": 38, "carbs": 40, "fiber": 7, "fat": 2}</t>
         </is>
       </c>
-      <c r="G21" t="n">
+      <c r="H21" t="n">
         <v>4</v>
       </c>
-      <c r="H21" t="n">
+      <c r="I21" t="n">
         <v>15</v>
       </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J21" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K21" t="inlineStr">
+      <c r="L21" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L21" t="inlineStr">
+      <c r="M21" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M21" t="inlineStr">
+      <c r="N21" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N21" t="b">
-        <v>0</v>
-      </c>
       <c r="O21" t="b">
         <v>0</v>
       </c>
-      <c r="P21" t="inlineStr"/>
-      <c r="Q21" t="inlineStr">
+      <c r="P21" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="inlineStr"/>
+      <c r="R21" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="inlineStr"/>
-      <c r="T21" t="inlineStr">
+      <c r="S21" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" t="inlineStr"/>
+      <c r="U21" t="inlineStr">
         <is>
           <t>1. Cook shrimp in a non-stick pan for 5 minutes with lime juice, cilantro, and salt.
 2. Serve over cooked quinoa.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U21" t="inlineStr"/>
-      <c r="V21" t="inlineStr">
+      <c r="V21" t="inlineStr"/>
+      <c r="W21" t="inlineStr">
         <is>
           <t>['Cook shrimp in a non-stick pan for 5 minutes with lime juice, cilantro, and salt.', 'Serve over cooked quinoa.', 'Cook time: 5 MINS']</t>
         </is>
@@ -2480,10 +2585,15 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
+          <t>4510</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '4 corn tortillas', '1 avocado, mashed', '1 teaspoon lime juice', '1 teaspoon smoked paprika', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E22" t="inlineStr">
+      <c r="F22" t="inlineStr">
         <is>
           <t>1. Bake tortillas at 375°F for 10 minutes until crispy.
 2. In a non-stick pan, cook shrimp with lime juice, paprika, and salt for 5 minutes.
@@ -2491,59 +2601,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F22" t="inlineStr">
+      <c r="G22" t="inlineStr">
         <is>
           <t>{"calories": 320, "protein": 38, "carbs": 30, "fiber": 6, "fat": 7}</t>
         </is>
       </c>
-      <c r="G22" t="n">
+      <c r="H22" t="n">
         <v>4</v>
       </c>
-      <c r="H22" t="n">
+      <c r="I22" t="n">
         <v>15</v>
       </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J22" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K22" t="inlineStr">
+      <c r="L22" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M22" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N22" t="b">
-        <v>0</v>
-      </c>
       <c r="O22" t="b">
         <v>0</v>
       </c>
-      <c r="P22" t="inlineStr"/>
-      <c r="Q22" t="inlineStr">
+      <c r="P22" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q22" t="inlineStr"/>
+      <c r="R22" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R22" t="n">
-        <v>0</v>
-      </c>
-      <c r="S22" t="inlineStr"/>
-      <c r="T22" t="inlineStr">
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="inlineStr"/>
+      <c r="U22" t="inlineStr">
         <is>
           <t>1. Bake tortillas at 375°F for 10 minutes until crispy.
 2. In a non-stick pan, cook shrimp with lime juice, paprika, and salt for 5 minutes.
@@ -2551,8 +2661,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U22" t="inlineStr"/>
-      <c r="V22" t="inlineStr">
+      <c r="V22" t="inlineStr"/>
+      <c r="W22" t="inlineStr">
         <is>
           <t>['Bake tortillas at 375°F for 10 minutes until crispy.', 'In a non-stick pan, cook shrimp with lime juice, paprika, and salt for 5 minutes.', 'Spread mashed avocado on tortillas and top with shrimp.', 'Cook time: 5 MINS']</t>
         </is>
@@ -2576,10 +2686,15 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
+          <t>4511</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
           <t>['2 cans sardines (low-mercury, packed in water)', '8 oz whole wheat pasta', '2 cloves garlic, minced', '1 teaspoon lemon juice', '1 teaspoon parsley', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E23" t="inlineStr">
+      <c r="F23" t="inlineStr">
         <is>
           <t>1. Cook pasta according to package instructions.
 2. In a non-stick pan, heat sardines with garlic, lemon juice, parsley, and salt for 5 minutes.
@@ -2587,59 +2702,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F23" t="inlineStr">
+      <c r="G23" t="inlineStr">
         <is>
           <t>{"calories": 380, "protein": 40, "carbs": 50, "fiber": 6, "fat": 8}</t>
         </is>
       </c>
-      <c r="G23" t="n">
+      <c r="H23" t="n">
         <v>4</v>
       </c>
-      <c r="H23" t="n">
+      <c r="I23" t="n">
         <v>20</v>
       </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J23" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'pasta', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K23" t="inlineStr">
+      <c r="L23" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L23" t="inlineStr">
+      <c r="M23" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M23" t="inlineStr">
+      <c r="N23" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N23" t="b">
-        <v>0</v>
-      </c>
       <c r="O23" t="b">
         <v>0</v>
       </c>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="inlineStr">
+      <c r="P23" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q23" t="inlineStr"/>
+      <c r="R23" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R23" t="n">
-        <v>0</v>
-      </c>
-      <c r="S23" t="inlineStr"/>
-      <c r="T23" t="inlineStr">
+      <c r="S23" t="n">
+        <v>0</v>
+      </c>
+      <c r="T23" t="inlineStr"/>
+      <c r="U23" t="inlineStr">
         <is>
           <t>1. Cook pasta according to package instructions.
 2. In a non-stick pan, heat sardines with garlic, lemon juice, parsley, and salt for 5 minutes.
@@ -2647,8 +2762,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U23" t="inlineStr"/>
-      <c r="V23" t="inlineStr">
+      <c r="V23" t="inlineStr"/>
+      <c r="W23" t="inlineStr">
         <is>
           <t>['Cook pasta according to package instructions.', 'In a non-stick pan, heat sardines with garlic, lemon juice, parsley, and salt for 5 minutes.', 'Toss sardine mixture with cooked pasta and serve.', 'Cook time: 5 MINS']</t>
         </is>
@@ -2667,15 +2782,20 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Oil-Free Baked Trout with Roasted Vegetables</t>
+          <t>Oil-Free Baked Trout With Roasted Vegetables</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
+          <t>4512</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
           <t>['4 trout fillets', '1 cup chopped zucchini', '1 cup chopped bell peppers', '1 teaspoon dried oregano', '1 teaspoon lemon juice', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E24" t="inlineStr">
+      <c r="F24" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place trout fillets and vegetables on parchment paper.
@@ -2684,59 +2804,59 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F24" t="inlineStr">
+      <c r="G24" t="inlineStr">
         <is>
           <t>{"calories": 320, "protein": 40, "carbs": 10, "fiber": 4, "fat": 12}</t>
         </is>
       </c>
-      <c r="G24" t="n">
+      <c r="H24" t="n">
         <v>4</v>
       </c>
-      <c r="H24" t="n">
+      <c r="I24" t="n">
         <v>20</v>
       </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J24" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K24" t="inlineStr">
+      <c r="L24" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L24" t="inlineStr">
+      <c r="M24" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M24" t="inlineStr">
+      <c r="N24" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N24" t="b">
-        <v>0</v>
-      </c>
       <c r="O24" t="b">
         <v>0</v>
       </c>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="inlineStr">
+      <c r="P24" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="inlineStr"/>
+      <c r="R24" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R24" t="n">
-        <v>0</v>
-      </c>
-      <c r="S24" t="inlineStr"/>
-      <c r="T24" t="inlineStr">
+      <c r="S24" t="n">
+        <v>0</v>
+      </c>
+      <c r="T24" t="inlineStr"/>
+      <c r="U24" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place trout fillets and vegetables on parchment paper.
@@ -2745,8 +2865,8 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U24" t="inlineStr"/>
-      <c r="V24" t="inlineStr">
+      <c r="V24" t="inlineStr"/>
+      <c r="W24" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place trout fillets and vegetables on parchment paper.', 'Rub trout with lemon juice, oregano, and salt.', 'Bake for 15 minutes until flaky.', 'Cook time: 15 MINS']</t>
         </is>
@@ -2770,77 +2890,82 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
+          <t>4513</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '1 cup cooked brown rice', '1 teaspoon lime juice', '1 teaspoon smoked paprika', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E25" t="inlineStr">
+      <c r="F25" t="inlineStr">
         <is>
           <t>1. Heat shrimp in a non-stick pan with lime juice, paprika, and salt.
 2. Serve over cooked brown rice.
 3. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="F25" t="inlineStr">
+      <c r="G25" t="inlineStr">
         <is>
           <t>{"calories": 320, "protein": 38, "carbs": 40, "fiber": 6, "fat": 2}</t>
         </is>
       </c>
-      <c r="G25" t="n">
+      <c r="H25" t="n">
         <v>4</v>
       </c>
-      <c r="H25" t="n">
+      <c r="I25" t="n">
         <v>15</v>
       </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J25" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K25" t="inlineStr">
+      <c r="L25" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M25" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N25" t="b">
-        <v>0</v>
-      </c>
       <c r="O25" t="b">
         <v>0</v>
       </c>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="inlineStr">
+      <c r="P25" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q25" t="inlineStr"/>
+      <c r="R25" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R25" t="n">
-        <v>0</v>
-      </c>
-      <c r="S25" t="inlineStr"/>
-      <c r="T25" t="inlineStr">
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr"/>
+      <c r="U25" t="inlineStr">
         <is>
           <t>1. Heat shrimp in a non-stick pan with lime juice, paprika, and salt.
 2. Serve over cooked brown rice.
 3. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="U25" t="inlineStr"/>
-      <c r="V25" t="inlineStr">
+      <c r="V25" t="inlineStr"/>
+      <c r="W25" t="inlineStr">
         <is>
           <t>['Heat shrimp in a non-stick pan with lime juice, paprika, and salt.', 'Serve over cooked brown rice.', 'Cook time: 10 MINS']</t>
         </is>
@@ -2864,10 +2989,15 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
+          <t>4514</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
           <t>['4 lobster tails', '1 teaspoon lemon juice', '2 cloves garlic, minced', '1 teaspoon chopped parsley', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E26" t="inlineStr">
+      <c r="F26" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place lobster tails on parchment paper and coat with lemon juice, garlic, parsley, and salt.
@@ -2875,59 +3005,59 @@
 4. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F26" t="inlineStr">
+      <c r="G26" t="inlineStr">
         <is>
           <t>{"calories": 290, "protein": 40, "carbs": 2, "fiber": 0, "fat": 2}</t>
         </is>
       </c>
-      <c r="G26" t="n">
+      <c r="H26" t="n">
         <v>4</v>
       </c>
-      <c r="H26" t="n">
+      <c r="I26" t="n">
         <v>20</v>
       </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J26" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K26" t="inlineStr">
+      <c r="L26" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
+      <c r="M26" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M26" t="inlineStr">
+      <c r="N26" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N26" t="b">
-        <v>0</v>
-      </c>
       <c r="O26" t="b">
         <v>0</v>
       </c>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="inlineStr">
+      <c r="P26" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q26" t="inlineStr"/>
+      <c r="R26" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R26" t="n">
-        <v>0</v>
-      </c>
-      <c r="S26" t="inlineStr"/>
-      <c r="T26" t="inlineStr">
+      <c r="S26" t="n">
+        <v>0</v>
+      </c>
+      <c r="T26" t="inlineStr"/>
+      <c r="U26" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place lobster tails on parchment paper and coat with lemon juice, garlic, parsley, and salt.
@@ -2935,8 +3065,8 @@
 4. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U26" t="inlineStr"/>
-      <c r="V26" t="inlineStr">
+      <c r="V26" t="inlineStr"/>
+      <c r="W26" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place lobster tails on parchment paper and coat with lemon juice, garlic, parsley, and salt.', 'Bake for 15 minutes.', 'Cook time: 15 MINS']</t>
         </is>
@@ -2955,15 +3085,20 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Oil-Free Grilled Scallops with Lemon &amp; Herbs</t>
+          <t>Oil-Free Grilled Scallops With Lemon &amp; Herbs</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
+          <t>4515</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
           <t>['1 pound scallops', '1 teaspoon lemon juice', '1 teaspoon dried basil', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E27" t="inlineStr">
+      <c r="F27" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan.
 2. Coat scallops with lemon juice, basil, and salt.
@@ -2971,59 +3106,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F27" t="inlineStr">
+      <c r="G27" t="inlineStr">
         <is>
           <t>{"calories": 250, "protein": 42, "carbs": 2, "fiber": 0, "fat": 1}</t>
         </is>
       </c>
-      <c r="G27" t="n">
+      <c r="H27" t="n">
         <v>4</v>
       </c>
-      <c r="H27" t="n">
+      <c r="I27" t="n">
         <v>10</v>
       </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J27" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K27" t="inlineStr">
+      <c r="L27" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
+      <c r="M27" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M27" t="inlineStr">
+      <c r="N27" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N27" t="b">
-        <v>0</v>
-      </c>
       <c r="O27" t="b">
         <v>0</v>
       </c>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="inlineStr">
+      <c r="P27" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q27" t="inlineStr"/>
+      <c r="R27" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R27" t="n">
-        <v>0</v>
-      </c>
-      <c r="S27" t="inlineStr"/>
-      <c r="T27" t="inlineStr">
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan.
 2. Coat scallops with lemon juice, basil, and salt.
@@ -3031,8 +3166,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U27" t="inlineStr"/>
-      <c r="V27" t="inlineStr">
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr">
         <is>
           <t>['Preheat grill or grill pan.', 'Coat scallops with lemon juice, basil, and salt.', 'Grill for 2 minutes per side until golden.', 'Cook time: 5 MINS']</t>
         </is>
@@ -3051,15 +3186,20 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oil-Free Baked Cod with Tomatoes &amp; Basil</t>
+          <t>Oil-Free Baked Cod With Tomatoes &amp; Basil</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
+          <t>4516</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
           <t>['4 cod fillets', '1 cup diced tomatoes', '1 teaspoon dried basil', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E28" t="inlineStr">
+      <c r="F28" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place cod fillets on parchment paper.
@@ -3068,59 +3208,59 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F28" t="inlineStr">
+      <c r="G28" t="inlineStr">
         <is>
           <t>{"calories": 200, "protein": 40, "carbs": 4, "fiber": 1, "fat": 1}</t>
         </is>
       </c>
-      <c r="G28" t="n">
+      <c r="H28" t="n">
         <v>4</v>
       </c>
-      <c r="H28" t="n">
+      <c r="I28" t="n">
         <v>20</v>
       </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J28" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K28" t="inlineStr">
+      <c r="L28" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
+      <c r="M28" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M28" t="inlineStr">
+      <c r="N28" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N28" t="b">
-        <v>0</v>
-      </c>
       <c r="O28" t="b">
         <v>0</v>
       </c>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="inlineStr">
+      <c r="P28" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q28" t="inlineStr"/>
+      <c r="R28" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R28" t="n">
-        <v>0</v>
-      </c>
-      <c r="S28" t="inlineStr"/>
-      <c r="T28" t="inlineStr">
+      <c r="S28" t="n">
+        <v>0</v>
+      </c>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place cod fillets on parchment paper.
@@ -3129,8 +3269,8 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U28" t="inlineStr"/>
-      <c r="V28" t="inlineStr">
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place cod fillets on parchment paper.', 'Top with tomatoes, basil, and salt.', 'Bake for 15 minutes.', 'Cook time: 15 MINS']</t>
         </is>
@@ -3154,10 +3294,15 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
+          <t>4517</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
           <t>['4 salmon fillets', '1 cup cooked brown rice', '1 teaspoon lemon juice', '2 cloves garlic, minced', '1 teaspoon chopped parsley', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E29" t="inlineStr">
+      <c r="F29" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place salmon on parchment paper, rub with lemon juice, garlic, parsley, and salt.
@@ -3166,59 +3311,59 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F29" t="inlineStr">
+      <c r="G29" t="inlineStr">
         <is>
           <t>{"calories": 350, "protein": 42, "carbs": 38, "fiber": 6, "fat": 10}</t>
         </is>
       </c>
-      <c r="G29" t="n">
+      <c r="H29" t="n">
         <v>4</v>
       </c>
-      <c r="H29" t="n">
+      <c r="I29" t="n">
         <v>20</v>
       </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J29" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K29" t="inlineStr">
+      <c r="L29" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
+      <c r="M29" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M29" t="inlineStr">
+      <c r="N29" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N29" t="b">
-        <v>0</v>
-      </c>
       <c r="O29" t="b">
         <v>0</v>
       </c>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="inlineStr">
+      <c r="P29" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q29" t="inlineStr"/>
+      <c r="R29" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R29" t="n">
-        <v>0</v>
-      </c>
-      <c r="S29" t="inlineStr"/>
-      <c r="T29" t="inlineStr">
+      <c r="S29" t="n">
+        <v>0</v>
+      </c>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place salmon on parchment paper, rub with lemon juice, garlic, parsley, and salt.
@@ -3227,8 +3372,8 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U29" t="inlineStr"/>
-      <c r="V29" t="inlineStr">
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place salmon on parchment paper, rub with lemon juice, garlic, parsley, and salt.', 'Bake for 15 minutes.', 'Serve over cooked brown rice.', 'Cook time: 15 MINS']</t>
         </is>
@@ -3252,10 +3397,15 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
+          <t>4518</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '4 whole wheat tortillas', '1 teaspoon lime juice', '1 teaspoon smoked paprika', '1/2 teaspoon salt', '1/2 cup shredded cabbage']</t>
         </is>
       </c>
-      <c r="E30" t="inlineStr">
+      <c r="F30" t="inlineStr">
         <is>
           <t>1. Heat a grill or non-stick pan.
 2. Toss shrimp with lime juice, paprika, and salt. Cook for 5 minutes.
@@ -3263,59 +3413,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F30" t="inlineStr">
+      <c r="G30" t="inlineStr">
         <is>
           <t>{"calories": 320, "protein": 40, "carbs": 38, "fiber": 7, "fat": 2}</t>
         </is>
       </c>
-      <c r="G30" t="n">
+      <c r="H30" t="n">
         <v>4</v>
       </c>
-      <c r="H30" t="n">
+      <c r="I30" t="n">
         <v>15</v>
       </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J30" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss', 'wraps']</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K30" t="inlineStr">
+      <c r="L30" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M30" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N30" t="b">
-        <v>0</v>
-      </c>
       <c r="O30" t="b">
         <v>0</v>
       </c>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="inlineStr">
+      <c r="P30" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q30" t="inlineStr"/>
+      <c r="R30" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R30" t="n">
-        <v>0</v>
-      </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr">
+      <c r="S30" t="n">
+        <v>0</v>
+      </c>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr">
         <is>
           <t>1. Heat a grill or non-stick pan.
 2. Toss shrimp with lime juice, paprika, and salt. Cook for 5 minutes.
@@ -3323,8 +3473,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr"/>
-      <c r="V30" t="inlineStr">
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr">
         <is>
           <t>['Heat a grill or non-stick pan.', 'Toss shrimp with lime juice, paprika, and salt. Cook for 5 minutes.', 'Fill tortillas with shrimp and cabbage, then wrap.', 'Cook time: 5 MINS']</t>
         </is>
@@ -3348,10 +3498,15 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
+          <t>4519</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
           <t>['4 tilapia fillets', '8 corn tortillas', '1 teaspoon lime juice', '1 teaspoon cumin', '1/2 teaspoon salt', '1/2 cup diced tomatoes']</t>
         </is>
       </c>
-      <c r="E31" t="inlineStr">
+      <c r="F31" t="inlineStr">
         <is>
           <t>1. Heat a grill or non-stick pan.
 2. Cook tilapia with lime juice, cumin, and salt for 5 minutes per side.
@@ -3359,59 +3514,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F31" t="inlineStr">
+      <c r="G31" t="inlineStr">
         <is>
           <t>{"calories": 280, "protein": 40, "carbs": 35, "fiber": 6, "fat": 2}</t>
         </is>
       </c>
-      <c r="G31" t="n">
+      <c r="H31" t="n">
         <v>4</v>
       </c>
-      <c r="H31" t="n">
+      <c r="I31" t="n">
         <v>15</v>
       </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J31" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K31" t="inlineStr">
+      <c r="L31" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
+      <c r="M31" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M31" t="inlineStr">
+      <c r="N31" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N31" t="b">
-        <v>0</v>
-      </c>
       <c r="O31" t="b">
         <v>0</v>
       </c>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="inlineStr">
+      <c r="P31" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q31" t="inlineStr"/>
+      <c r="R31" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R31" t="n">
-        <v>0</v>
-      </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr">
+      <c r="S31" t="n">
+        <v>0</v>
+      </c>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr">
         <is>
           <t>1. Heat a grill or non-stick pan.
 2. Cook tilapia with lime juice, cumin, and salt for 5 minutes per side.
@@ -3419,8 +3574,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr"/>
-      <c r="V31" t="inlineStr">
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr">
         <is>
           <t>['Heat a grill or non-stick pan.', 'Cook tilapia with lime juice, cumin, and salt for 5 minutes per side.', 'Serve on tortillas with diced tomatoes.', 'Cook time: 5 MINS']</t>
         </is>
@@ -3439,82 +3594,87 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oil-Free Mussels in Tomato Broth</t>
+          <t>Oil-Free Mussels In Tomato Broth</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
+          <t>4520</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
           <t>['2 pounds mussels, cleaned', '4 cups vegetable broth', '1 cup diced tomatoes', '2 cloves garlic, minced', '1 teaspoon dried basil', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E32" t="inlineStr">
+      <c r="F32" t="inlineStr">
         <is>
           <t>1. Bring broth, tomatoes, garlic, basil, and salt to a boil.
 2. Add mussels, cover, and steam for 5 minutes until shells open.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F32" t="inlineStr">
+      <c r="G32" t="inlineStr">
         <is>
           <t>{"calories": 250, "protein": 42, "carbs": 10, "fiber": 2, "fat": 2}</t>
         </is>
       </c>
-      <c r="G32" t="n">
+      <c r="H32" t="n">
         <v>4</v>
       </c>
-      <c r="H32" t="n">
+      <c r="I32" t="n">
         <v>15</v>
       </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J32" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K32" t="inlineStr">
+      <c r="L32" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
+      <c r="M32" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M32" t="inlineStr">
+      <c r="N32" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N32" t="b">
-        <v>0</v>
-      </c>
       <c r="O32" t="b">
         <v>0</v>
       </c>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="inlineStr">
+      <c r="P32" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q32" t="inlineStr"/>
+      <c r="R32" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R32" t="n">
-        <v>0</v>
-      </c>
-      <c r="S32" t="inlineStr"/>
-      <c r="T32" t="inlineStr">
+      <c r="S32" t="n">
+        <v>0</v>
+      </c>
+      <c r="T32" t="inlineStr"/>
+      <c r="U32" t="inlineStr">
         <is>
           <t>1. Bring broth, tomatoes, garlic, basil, and salt to a boil.
 2. Add mussels, cover, and steam for 5 minutes until shells open.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U32" t="inlineStr"/>
-      <c r="V32" t="inlineStr">
+      <c r="V32" t="inlineStr"/>
+      <c r="W32" t="inlineStr">
         <is>
           <t>['Bring broth, tomatoes, garlic, basil, and salt to a boil.', 'Add mussels, cover, and steam for 5 minutes until shells open.', 'Cook time: 5 MINS']</t>
         </is>
@@ -3538,10 +3698,15 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
+          <t>4521</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
           <t>['2 cans sardines (low-mercury, packed in water)', '2 avocados, mashed', '4 slices whole wheat bread', '1 teaspoon lime juice', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E33" t="inlineStr">
+      <c r="F33" t="inlineStr">
         <is>
           <t>1. Toast whole wheat bread.
 2. Spread mashed avocado on each slice.
@@ -3549,59 +3714,59 @@
 4. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="F33" t="inlineStr">
+      <c r="G33" t="inlineStr">
         <is>
           <t>{"calories": 320, "protein": 40, "carbs": 35, "fiber": 8, "fat": 10}</t>
         </is>
       </c>
-      <c r="G33" t="n">
+      <c r="H33" t="n">
         <v>4</v>
       </c>
-      <c r="H33" t="n">
+      <c r="I33" t="n">
         <v>10</v>
       </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J33" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K33" t="inlineStr">
+      <c r="L33" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L33" t="inlineStr">
+      <c r="M33" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M33" t="inlineStr">
+      <c r="N33" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N33" t="b">
-        <v>0</v>
-      </c>
       <c r="O33" t="b">
         <v>0</v>
       </c>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="inlineStr">
+      <c r="P33" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q33" t="inlineStr"/>
+      <c r="R33" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R33" t="n">
-        <v>0</v>
-      </c>
-      <c r="S33" t="inlineStr"/>
-      <c r="T33" t="inlineStr">
+      <c r="S33" t="n">
+        <v>0</v>
+      </c>
+      <c r="T33" t="inlineStr"/>
+      <c r="U33" t="inlineStr">
         <is>
           <t>1. Toast whole wheat bread.
 2. Spread mashed avocado on each slice.
@@ -3609,8 +3774,8 @@
 4. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="U33" t="inlineStr"/>
-      <c r="V33" t="inlineStr">
+      <c r="V33" t="inlineStr"/>
+      <c r="W33" t="inlineStr">
         <is>
           <t>['Toast whole wheat bread.', 'Spread mashed avocado on each slice.', 'Top with sardines, lime juice, and salt.', 'Cook time: 10 MINS']</t>
         </is>
@@ -3634,10 +3799,15 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
+          <t>4522</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
           <t>['4 salmon fillets', '1 teaspoon smoked paprika', '1 teaspoon lime juice', '1/2 teaspoon salt', '1 teaspoon chopped cilantro']</t>
         </is>
       </c>
-      <c r="E34" t="inlineStr">
+      <c r="F34" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan.
 2. Rub salmon with smoked paprika, lime juice, salt, and cilantro.
@@ -3645,59 +3815,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F34" t="inlineStr">
+      <c r="G34" t="inlineStr">
         <is>
           <t>{"calories": 310, "protein": 40, "carbs": 2, "fiber": 0, "fat": 10}</t>
         </is>
       </c>
-      <c r="G34" t="n">
+      <c r="H34" t="n">
         <v>4</v>
       </c>
-      <c r="H34" t="n">
+      <c r="I34" t="n">
         <v>15</v>
       </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J34" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K34" t="inlineStr">
+      <c r="L34" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L34" t="inlineStr">
+      <c r="M34" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M34" t="inlineStr">
+      <c r="N34" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N34" t="b">
-        <v>0</v>
-      </c>
       <c r="O34" t="b">
         <v>0</v>
       </c>
-      <c r="P34" t="inlineStr"/>
-      <c r="Q34" t="inlineStr">
+      <c r="P34" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q34" t="inlineStr"/>
+      <c r="R34" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R34" t="n">
-        <v>0</v>
-      </c>
-      <c r="S34" t="inlineStr"/>
-      <c r="T34" t="inlineStr">
+      <c r="S34" t="n">
+        <v>0</v>
+      </c>
+      <c r="T34" t="inlineStr"/>
+      <c r="U34" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan.
 2. Rub salmon with smoked paprika, lime juice, salt, and cilantro.
@@ -3705,8 +3875,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U34" t="inlineStr"/>
-      <c r="V34" t="inlineStr">
+      <c r="V34" t="inlineStr"/>
+      <c r="W34" t="inlineStr">
         <is>
           <t>['Preheat grill or grill pan.', 'Rub salmon with smoked paprika, lime juice, salt, and cilantro.', 'Grill for 4 minutes per side until fully cooked.', 'Cook time: 5 MINS']</t>
         </is>
@@ -3730,10 +3900,15 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
+          <t>4523</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
           <t>['4 tilapia fillets', '1 cup diced tomatoes', '1/4 cup chopped green olives', '1 teaspoon oregano', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E35" t="inlineStr">
+      <c r="F35" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place tilapia fillets in a baking dish.
@@ -3742,59 +3917,59 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
+      <c r="G35" t="inlineStr">
         <is>
           <t>{"calories": 280, "protein": 42, "carbs": 8, "fiber": 2, "fat": 2}</t>
         </is>
       </c>
-      <c r="G35" t="n">
+      <c r="H35" t="n">
         <v>4</v>
       </c>
-      <c r="H35" t="n">
+      <c r="I35" t="n">
         <v>20</v>
       </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K35" t="inlineStr">
+      <c r="L35" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L35" t="inlineStr">
+      <c r="M35" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M35" t="inlineStr">
+      <c r="N35" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N35" t="b">
-        <v>0</v>
-      </c>
       <c r="O35" t="b">
         <v>0</v>
       </c>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="inlineStr">
+      <c r="P35" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q35" t="inlineStr"/>
+      <c r="R35" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R35" t="n">
-        <v>0</v>
-      </c>
-      <c r="S35" t="inlineStr"/>
-      <c r="T35" t="inlineStr">
+      <c r="S35" t="n">
+        <v>0</v>
+      </c>
+      <c r="T35" t="inlineStr"/>
+      <c r="U35" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place tilapia fillets in a baking dish.
@@ -3803,8 +3978,8 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U35" t="inlineStr"/>
-      <c r="V35" t="inlineStr">
+      <c r="V35" t="inlineStr"/>
+      <c r="W35" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place tilapia fillets in a baking dish.', 'Top with tomatoes, olives, oregano, and salt.', 'Bake for 15 minutes until flaky.', 'Cook time: 15 MINS']</t>
         </is>
@@ -3828,77 +4003,82 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
+          <t>4524</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '8 corn tortillas', '1/2 cup cooked black beans', '1 teaspoon lime juice', '1 teaspoon cumin', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E36" t="inlineStr">
+      <c r="F36" t="inlineStr">
         <is>
           <t>1. Heat shrimp in a non-stick pan with lime juice, cumin, and salt.
 2. Serve in tortillas with black beans.
 3. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="F36" t="inlineStr">
+      <c r="G36" t="inlineStr">
         <is>
           <t>{"calories": 320, "protein": 38, "carbs": 38, "fiber": 6, "fat": 2}</t>
         </is>
       </c>
-      <c r="G36" t="n">
+      <c r="H36" t="n">
         <v>4</v>
       </c>
-      <c r="H36" t="n">
+      <c r="I36" t="n">
         <v>15</v>
       </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J36" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K36" t="inlineStr">
+      <c r="L36" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
+      <c r="M36" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M36" t="inlineStr">
+      <c r="N36" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N36" t="b">
-        <v>0</v>
-      </c>
       <c r="O36" t="b">
         <v>0</v>
       </c>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="inlineStr">
+      <c r="P36" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q36" t="inlineStr"/>
+      <c r="R36" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R36" t="n">
-        <v>0</v>
-      </c>
-      <c r="S36" t="inlineStr"/>
-      <c r="T36" t="inlineStr">
+      <c r="S36" t="n">
+        <v>0</v>
+      </c>
+      <c r="T36" t="inlineStr"/>
+      <c r="U36" t="inlineStr">
         <is>
           <t>1. Heat shrimp in a non-stick pan with lime juice, cumin, and salt.
 2. Serve in tortillas with black beans.
 3. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="U36" t="inlineStr"/>
-      <c r="V36" t="inlineStr">
+      <c r="V36" t="inlineStr"/>
+      <c r="W36" t="inlineStr">
         <is>
           <t>['Heat shrimp in a non-stick pan with lime juice, cumin, and salt.', 'Serve in tortillas with black beans.', 'Cook time: 10 MINS']</t>
         </is>
@@ -3922,10 +4102,15 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
+          <t>4525</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
           <t>['4 mahi-mahi fillets', '1 teaspoon lemon juice', '2 cloves garlic, minced', '1 teaspoon dried oregano', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
+      <c r="F37" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place mahi-mahi fillets on a parchment-lined baking sheet.
@@ -3934,59 +4119,59 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F37" t="inlineStr">
+      <c r="G37" t="inlineStr">
         <is>
           <t>{"calories": 280, "protein": 42, "carbs": 2, "fiber": 0, "fat": 2}</t>
         </is>
       </c>
-      <c r="G37" t="n">
+      <c r="H37" t="n">
         <v>4</v>
       </c>
-      <c r="H37" t="n">
+      <c r="I37" t="n">
         <v>20</v>
       </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J37" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K37" t="inlineStr">
+      <c r="L37" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L37" t="inlineStr">
+      <c r="M37" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M37" t="inlineStr">
+      <c r="N37" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N37" t="b">
-        <v>0</v>
-      </c>
       <c r="O37" t="b">
         <v>0</v>
       </c>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="inlineStr">
+      <c r="P37" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q37" t="inlineStr"/>
+      <c r="R37" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R37" t="n">
-        <v>0</v>
-      </c>
-      <c r="S37" t="inlineStr"/>
-      <c r="T37" t="inlineStr">
+      <c r="S37" t="n">
+        <v>0</v>
+      </c>
+      <c r="T37" t="inlineStr"/>
+      <c r="U37" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place mahi-mahi fillets on a parchment-lined baking sheet.
@@ -3995,8 +4180,8 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U37" t="inlineStr"/>
-      <c r="V37" t="inlineStr">
+      <c r="V37" t="inlineStr"/>
+      <c r="W37" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place mahi-mahi fillets on a parchment-lined baking sheet.', 'Rub with lemon juice, garlic, oregano, and salt.', 'Bake for 15 minutes until flaky.', 'Cook time: 15 MINS']</t>
         </is>
@@ -4020,10 +4205,15 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
+          <t>4526</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
           <t>['8 fresh sardines, gutted and cleaned', '1 teaspoon lime juice', '1 teaspoon smoked paprika', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E38" t="inlineStr">
+      <c r="F38" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan.
 2. Rub sardines with lime juice, paprika, and salt.
@@ -4031,59 +4221,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F38" t="inlineStr">
+      <c r="G38" t="inlineStr">
         <is>
           <t>{"calories": 320, "protein": 42, "carbs": 2, "fiber": 0, "fat": 12}</t>
         </is>
       </c>
-      <c r="G38" t="n">
+      <c r="H38" t="n">
         <v>4</v>
       </c>
-      <c r="H38" t="n">
+      <c r="I38" t="n">
         <v>15</v>
       </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J38" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K38" t="inlineStr">
+      <c r="L38" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M38" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N38" t="b">
-        <v>0</v>
-      </c>
       <c r="O38" t="b">
         <v>0</v>
       </c>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="inlineStr">
+      <c r="P38" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q38" t="inlineStr"/>
+      <c r="R38" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R38" t="n">
-        <v>0</v>
-      </c>
-      <c r="S38" t="inlineStr"/>
-      <c r="T38" t="inlineStr">
+      <c r="S38" t="n">
+        <v>0</v>
+      </c>
+      <c r="T38" t="inlineStr"/>
+      <c r="U38" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan.
 2. Rub sardines with lime juice, paprika, and salt.
@@ -4091,8 +4281,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U38" t="inlineStr"/>
-      <c r="V38" t="inlineStr">
+      <c r="V38" t="inlineStr"/>
+      <c r="W38" t="inlineStr">
         <is>
           <t>['Preheat grill or grill pan.', 'Rub sardines with lime juice, paprika, and salt.', 'Grill for 4 minutes per side.', 'Cook time: 5 MINS']</t>
         </is>
@@ -4116,77 +4306,82 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
+          <t>4527</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
           <t>['1 pound cooked shrimp, chopped', '1 avocado, diced', '1/2 cup diced tomatoes', '1/4 cup diced red onion', '1 teaspoon lime juice', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E39" t="inlineStr">
+      <c r="F39" t="inlineStr">
         <is>
           <t>1. Mix shrimp, avocado, tomatoes, red onion, lime juice, and salt in a bowl.
 2. Serve chilled.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F39" t="inlineStr">
+      <c r="G39" t="inlineStr">
         <is>
           <t>{"calories": 280, "protein": 35, "carbs": 12, "fiber": 5, "fat": 7}</t>
         </is>
       </c>
-      <c r="G39" t="n">
+      <c r="H39" t="n">
         <v>4</v>
       </c>
-      <c r="H39" t="n">
+      <c r="I39" t="n">
         <v>20</v>
       </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K39" t="inlineStr">
+      <c r="L39" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L39" t="inlineStr">
+      <c r="M39" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M39" t="inlineStr">
+      <c r="N39" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N39" t="b">
-        <v>0</v>
-      </c>
       <c r="O39" t="b">
         <v>0</v>
       </c>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="inlineStr">
+      <c r="P39" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q39" t="inlineStr"/>
+      <c r="R39" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R39" t="n">
-        <v>0</v>
-      </c>
-      <c r="S39" t="inlineStr"/>
-      <c r="T39" t="inlineStr">
+      <c r="S39" t="n">
+        <v>0</v>
+      </c>
+      <c r="T39" t="inlineStr"/>
+      <c r="U39" t="inlineStr">
         <is>
           <t>1. Mix shrimp, avocado, tomatoes, red onion, lime juice, and salt in a bowl.
 2. Serve chilled.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U39" t="inlineStr"/>
-      <c r="V39" t="inlineStr">
+      <c r="V39" t="inlineStr"/>
+      <c r="W39" t="inlineStr">
         <is>
           <t>['Mix shrimp, avocado, tomatoes, red onion, lime juice, and salt in a bowl.', 'Serve chilled.', 'Cook time: 5 MINS']</t>
         </is>
@@ -4210,10 +4405,15 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
+          <t>4528</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
           <t>['1 pound scallops', '1 teaspoon chili powder', '1 teaspoon lime juice', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E40" t="inlineStr">
+      <c r="F40" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place scallops on a parchment-lined baking sheet.
@@ -4222,59 +4422,59 @@
 5. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
+      <c r="G40" t="inlineStr">
         <is>
           <t>{"calories": 250, "protein": 42, "carbs": 2, "fiber": 0, "fat": 1}</t>
         </is>
       </c>
-      <c r="G40" t="n">
+      <c r="H40" t="n">
         <v>4</v>
       </c>
-      <c r="H40" t="n">
+      <c r="I40" t="n">
         <v>15</v>
       </c>
-      <c r="I40" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J40" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K40" t="inlineStr">
+      <c r="L40" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M40" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N40" t="b">
-        <v>0</v>
-      </c>
       <c r="O40" t="b">
         <v>0</v>
       </c>
-      <c r="P40" t="inlineStr"/>
-      <c r="Q40" t="inlineStr">
+      <c r="P40" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q40" t="inlineStr"/>
+      <c r="R40" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R40" t="n">
-        <v>0</v>
-      </c>
-      <c r="S40" t="inlineStr"/>
-      <c r="T40" t="inlineStr">
+      <c r="S40" t="n">
+        <v>0</v>
+      </c>
+      <c r="T40" t="inlineStr"/>
+      <c r="U40" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place scallops on a parchment-lined baking sheet.
@@ -4283,8 +4483,8 @@
 5. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="U40" t="inlineStr"/>
-      <c r="V40" t="inlineStr">
+      <c r="V40" t="inlineStr"/>
+      <c r="W40" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place scallops on a parchment-lined baking sheet.', 'Coat with chili powder, lime juice, and salt.', 'Bake for 10 minutes.', 'Cook time: 10 MINS']</t>
         </is>
@@ -4308,10 +4508,15 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
+          <t>4529</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
           <t>['4 salmon fillets', '1 teaspoon lemon juice', '1 teaspoon dried basil', '1/2 teaspoon salt', '1/2 cup diced cucumbers', '1/2 cup diced tomatoes']</t>
         </is>
       </c>
-      <c r="E41" t="inlineStr">
+      <c r="F41" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place salmon on parchment paper, rub with lemon juice, basil, and salt.
@@ -4320,59 +4525,59 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F41" t="inlineStr">
+      <c r="G41" t="inlineStr">
         <is>
           <t>{"calories": 320, "protein": 40, "carbs": 10, "fiber": 3, "fat": 10}</t>
         </is>
       </c>
-      <c r="G41" t="n">
+      <c r="H41" t="n">
         <v>4</v>
       </c>
-      <c r="H41" t="n">
+      <c r="I41" t="n">
         <v>20</v>
       </c>
-      <c r="I41" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J41" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K41" t="inlineStr">
+      <c r="L41" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L41" t="inlineStr">
+      <c r="M41" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M41" t="inlineStr">
+      <c r="N41" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N41" t="b">
-        <v>0</v>
-      </c>
       <c r="O41" t="b">
         <v>0</v>
       </c>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="inlineStr">
+      <c r="P41" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q41" t="inlineStr"/>
+      <c r="R41" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R41" t="n">
-        <v>0</v>
-      </c>
-      <c r="S41" t="inlineStr"/>
-      <c r="T41" t="inlineStr">
+      <c r="S41" t="n">
+        <v>0</v>
+      </c>
+      <c r="T41" t="inlineStr"/>
+      <c r="U41" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place salmon on parchment paper, rub with lemon juice, basil, and salt.
@@ -4381,8 +4586,8 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U41" t="inlineStr"/>
-      <c r="V41" t="inlineStr">
+      <c r="V41" t="inlineStr"/>
+      <c r="W41" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place salmon on parchment paper, rub with lemon juice, basil, and salt.', 'Bake for 15 minutes.', 'Serve with cucumbers and tomatoes.', 'Cook time: 15 MINS']</t>
         </is>
@@ -4406,10 +4611,15 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
+          <t>4530</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
           <t>['4 halibut fillets', '1 teaspoon lemon juice', '2 cloves garlic, minced', '1 teaspoon dried parsley', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E42" t="inlineStr">
+      <c r="F42" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place halibut fillets on a parchment-lined baking sheet.
@@ -4418,59 +4628,59 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F42" t="inlineStr">
+      <c r="G42" t="inlineStr">
         <is>
           <t>{"calories": 280, "protein": 42, "carbs": 2, "fiber": 0, "fat": 2}</t>
         </is>
       </c>
-      <c r="G42" t="n">
+      <c r="H42" t="n">
         <v>4</v>
       </c>
-      <c r="H42" t="n">
+      <c r="I42" t="n">
         <v>20</v>
       </c>
-      <c r="I42" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J42" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K42" t="inlineStr">
+      <c r="L42" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L42" t="inlineStr">
+      <c r="M42" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M42" t="inlineStr">
+      <c r="N42" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N42" t="b">
-        <v>0</v>
-      </c>
       <c r="O42" t="b">
         <v>0</v>
       </c>
-      <c r="P42" t="inlineStr"/>
-      <c r="Q42" t="inlineStr">
+      <c r="P42" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q42" t="inlineStr"/>
+      <c r="R42" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R42" t="n">
-        <v>0</v>
-      </c>
-      <c r="S42" t="inlineStr"/>
-      <c r="T42" t="inlineStr">
+      <c r="S42" t="n">
+        <v>0</v>
+      </c>
+      <c r="T42" t="inlineStr"/>
+      <c r="U42" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place halibut fillets on a parchment-lined baking sheet.
@@ -4479,8 +4689,8 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U42" t="inlineStr"/>
-      <c r="V42" t="inlineStr">
+      <c r="V42" t="inlineStr"/>
+      <c r="W42" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place halibut fillets on a parchment-lined baking sheet.', 'Rub with lemon juice, garlic, parsley, and salt.', 'Bake for 15 minutes until flaky.', 'Cook time: 15 MINS']</t>
         </is>
@@ -4504,77 +4714,82 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
+          <t>4531</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '1 cup cooked quinoa', '1 teaspoon lime juice', '1 teaspoon chopped cilantro', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E43" t="inlineStr">
+      <c r="F43" t="inlineStr">
         <is>
           <t>1. Cook shrimp in a non-stick pan for 5 minutes with lime juice, cilantro, and salt.
 2. Serve over cooked quinoa.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F43" t="inlineStr">
+      <c r="G43" t="inlineStr">
         <is>
           <t>{"calories": 320, "protein": 38, "carbs": 40, "fiber": 7, "fat": 2}</t>
         </is>
       </c>
-      <c r="G43" t="n">
+      <c r="H43" t="n">
         <v>4</v>
       </c>
-      <c r="H43" t="n">
+      <c r="I43" t="n">
         <v>15</v>
       </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J43" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K43" t="inlineStr">
+      <c r="L43" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L43" t="inlineStr">
+      <c r="M43" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M43" t="inlineStr">
+      <c r="N43" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N43" t="b">
-        <v>0</v>
-      </c>
       <c r="O43" t="b">
         <v>0</v>
       </c>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="inlineStr">
+      <c r="P43" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q43" t="inlineStr"/>
+      <c r="R43" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R43" t="n">
-        <v>0</v>
-      </c>
-      <c r="S43" t="inlineStr"/>
-      <c r="T43" t="inlineStr">
+      <c r="S43" t="n">
+        <v>0</v>
+      </c>
+      <c r="T43" t="inlineStr"/>
+      <c r="U43" t="inlineStr">
         <is>
           <t>1. Cook shrimp in a non-stick pan for 5 minutes with lime juice, cilantro, and salt.
 2. Serve over cooked quinoa.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U43" t="inlineStr"/>
-      <c r="V43" t="inlineStr">
+      <c r="V43" t="inlineStr"/>
+      <c r="W43" t="inlineStr">
         <is>
           <t>['Cook shrimp in a non-stick pan for 5 minutes with lime juice, cilantro, and salt.', 'Serve over cooked quinoa.', 'Cook time: 5 MINS']</t>
         </is>
@@ -4598,10 +4813,15 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
+          <t>4532</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '8 corn tortillas', '1 teaspoon lime juice', '1 teaspoon chili powder', '1/2 teaspoon salt', '1/2 cup shredded cabbage']</t>
         </is>
       </c>
-      <c r="E44" t="inlineStr">
+      <c r="F44" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Add shrimp, lime juice, chili powder, and salt. Cook for 5 minutes.
@@ -4609,59 +4829,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F44" t="inlineStr">
+      <c r="G44" t="inlineStr">
         <is>
           <t>{"calories": 290, "protein": 36, "carbs": 38, "fiber": 6, "fat": 2}</t>
         </is>
       </c>
-      <c r="G44" t="n">
+      <c r="H44" t="n">
         <v>4</v>
       </c>
-      <c r="H44" t="n">
+      <c r="I44" t="n">
         <v>15</v>
       </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J44" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K44" t="inlineStr">
+      <c r="L44" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M44" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N44" t="b">
-        <v>0</v>
-      </c>
       <c r="O44" t="b">
         <v>0</v>
       </c>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="inlineStr">
+      <c r="P44" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q44" t="inlineStr"/>
+      <c r="R44" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R44" t="n">
-        <v>0</v>
-      </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr">
+      <c r="S44" t="n">
+        <v>0</v>
+      </c>
+      <c r="T44" t="inlineStr"/>
+      <c r="U44" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Add shrimp, lime juice, chili powder, and salt. Cook for 5 minutes.
@@ -4669,8 +4889,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U44" t="inlineStr"/>
-      <c r="V44" t="inlineStr">
+      <c r="V44" t="inlineStr"/>
+      <c r="W44" t="inlineStr">
         <is>
           <t>['Heat a non-stick pan over medium heat.', 'Add shrimp, lime juice, chili powder, and salt. Cook for 5 minutes.', 'Serve in warm tortillas with cabbage.', 'Cook time: 5 MINS']</t>
         </is>
@@ -4689,15 +4909,20 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Oil-Free Baked Cod with Garlic &amp; Dill</t>
+          <t>Oil-Free Baked Cod With Garlic &amp; Dill</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
+          <t>4533</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
           <t>['4 cod fillets', '1 teaspoon lemon juice', '2 cloves garlic, minced', '1 teaspoon dried dill', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E45" t="inlineStr">
+      <c r="F45" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place cod fillets on a parchment-lined baking sheet.
@@ -4706,59 +4931,59 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F45" t="inlineStr">
+      <c r="G45" t="inlineStr">
         <is>
           <t>{"calories": 200, "protein": 40, "carbs": 2, "fiber": 0, "fat": 1}</t>
         </is>
       </c>
-      <c r="G45" t="n">
+      <c r="H45" t="n">
         <v>4</v>
       </c>
-      <c r="H45" t="n">
+      <c r="I45" t="n">
         <v>20</v>
       </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K45" t="inlineStr">
+      <c r="L45" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L45" t="inlineStr">
+      <c r="M45" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M45" t="inlineStr">
+      <c r="N45" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N45" t="b">
-        <v>0</v>
-      </c>
       <c r="O45" t="b">
         <v>0</v>
       </c>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="inlineStr">
+      <c r="P45" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q45" t="inlineStr"/>
+      <c r="R45" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R45" t="n">
-        <v>0</v>
-      </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr">
+      <c r="S45" t="n">
+        <v>0</v>
+      </c>
+      <c r="T45" t="inlineStr"/>
+      <c r="U45" t="inlineStr">
         <is>
           <t>1. Preheat oven to 375°F.
 2. Place cod fillets on a parchment-lined baking sheet.
@@ -4767,8 +4992,8 @@
 5. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U45" t="inlineStr"/>
-      <c r="V45" t="inlineStr">
+      <c r="V45" t="inlineStr"/>
+      <c r="W45" t="inlineStr">
         <is>
           <t>['Preheat oven to 375°F.', 'Place cod fillets on a parchment-lined baking sheet.', 'Rub with lemon juice, garlic, dill, and salt.', 'Bake for 15 minutes until flaky.', 'Cook time: 15 MINS']</t>
         </is>
@@ -4787,15 +5012,20 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Oil-Free Grilled Tilapia with Roasted Vegetables</t>
+          <t>Oil-Free Grilled Tilapia With Roasted Vegetables</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
+          <t>4534</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
           <t>['4 tilapia fillets', '1 teaspoon lime juice', '1 teaspoon oregano', '1/2 teaspoon salt', '1 cup chopped zucchini', '1 cup cherry tomatoes']</t>
         </is>
       </c>
-      <c r="E46" t="inlineStr">
+      <c r="F46" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan.
 2. Rub tilapia with lime juice, oregano, and salt.
@@ -4804,59 +5034,59 @@
 5. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F46" t="inlineStr">
+      <c r="G46" t="inlineStr">
         <is>
           <t>{"calories": 270, "protein": 42, "carbs": 10, "fiber": 3, "fat": 2}</t>
         </is>
       </c>
-      <c r="G46" t="n">
+      <c r="H46" t="n">
         <v>4</v>
       </c>
-      <c r="H46" t="n">
+      <c r="I46" t="n">
         <v>20</v>
       </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J46" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K46" t="inlineStr">
+      <c r="L46" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L46" t="inlineStr">
+      <c r="M46" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M46" t="inlineStr">
+      <c r="N46" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N46" t="b">
-        <v>0</v>
-      </c>
       <c r="O46" t="b">
         <v>0</v>
       </c>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="inlineStr">
+      <c r="P46" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q46" t="inlineStr"/>
+      <c r="R46" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R46" t="n">
-        <v>0</v>
-      </c>
-      <c r="S46" t="inlineStr"/>
-      <c r="T46" t="inlineStr">
+      <c r="S46" t="n">
+        <v>0</v>
+      </c>
+      <c r="T46" t="inlineStr"/>
+      <c r="U46" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan.
 2. Rub tilapia with lime juice, oregano, and salt.
@@ -4865,8 +5095,8 @@
 5. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U46" t="inlineStr"/>
-      <c r="V46" t="inlineStr">
+      <c r="V46" t="inlineStr"/>
+      <c r="W46" t="inlineStr">
         <is>
           <t>['Preheat grill or grill pan.', 'Rub tilapia with lime juice, oregano, and salt.', 'Grill for 5 minutes per side.', 'Serve with grilled zucchini and cherry tomatoes.', 'Cook time: 5 MINS']</t>
         </is>
@@ -4890,10 +5120,15 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
+          <t>4535</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
           <t>['2 cans sardines (low-mercury, packed in water)', '1/2 cup diced cucumbers', '1/2 cup diced tomatoes', '1 teaspoon lime juice', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E47" t="inlineStr">
+      <c r="F47" t="inlineStr">
         <is>
           <t>1. Drain sardines and mash in a bowl.
 2. Mix with cucumbers, tomatoes, lime juice, and salt.
@@ -4901,59 +5136,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F47" t="inlineStr">
+      <c r="G47" t="inlineStr">
         <is>
           <t>{"calories": 250, "protein": 32, "carbs": 6, "fiber": 2, "fat": 8}</t>
         </is>
       </c>
-      <c r="G47" t="n">
+      <c r="H47" t="n">
         <v>4</v>
       </c>
-      <c r="H47" t="n">
+      <c r="I47" t="n">
         <v>10</v>
       </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J47" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'salads', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K47" t="inlineStr">
+      <c r="L47" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L47" t="inlineStr">
+      <c r="M47" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M47" t="inlineStr">
+      <c r="N47" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N47" t="b">
-        <v>0</v>
-      </c>
       <c r="O47" t="b">
         <v>0</v>
       </c>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="inlineStr">
+      <c r="P47" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q47" t="inlineStr"/>
+      <c r="R47" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R47" t="n">
-        <v>0</v>
-      </c>
-      <c r="S47" t="inlineStr"/>
-      <c r="T47" t="inlineStr">
+      <c r="S47" t="n">
+        <v>0</v>
+      </c>
+      <c r="T47" t="inlineStr"/>
+      <c r="U47" t="inlineStr">
         <is>
           <t>1. Drain sardines and mash in a bowl.
 2. Mix with cucumbers, tomatoes, lime juice, and salt.
@@ -4961,8 +5196,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U47" t="inlineStr"/>
-      <c r="V47" t="inlineStr">
+      <c r="V47" t="inlineStr"/>
+      <c r="W47" t="inlineStr">
         <is>
           <t>['Drain sardines and mash in a bowl.', 'Mix with cucumbers, tomatoes, lime juice, and salt.', 'Serve chilled or at room temperature.', 'Cook time: 5 MINS']</t>
         </is>
@@ -4986,77 +5221,82 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
+          <t>4536</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '1 cup cooked corn', '1 teaspoon lime juice', '1 teaspoon smoked paprika', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr">
+      <c r="F48" t="inlineStr">
         <is>
           <t>1. Heat shrimp in a non-stick pan with lime juice, paprika, and salt for 5 minutes.
 2. Serve over cooked corn.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F48" t="inlineStr">
+      <c r="G48" t="inlineStr">
         <is>
           <t>{"calories": 290, "protein": 38, "carbs": 32, "fiber": 5, "fat": 2}</t>
         </is>
       </c>
-      <c r="G48" t="n">
+      <c r="H48" t="n">
         <v>4</v>
       </c>
-      <c r="H48" t="n">
+      <c r="I48" t="n">
         <v>15</v>
       </c>
-      <c r="I48" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J48" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K48" t="inlineStr">
+      <c r="L48" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M48" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N48" t="b">
-        <v>0</v>
-      </c>
       <c r="O48" t="b">
         <v>0</v>
       </c>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="inlineStr">
+      <c r="P48" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q48" t="inlineStr"/>
+      <c r="R48" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R48" t="n">
-        <v>0</v>
-      </c>
-      <c r="S48" t="inlineStr"/>
-      <c r="T48" t="inlineStr">
+      <c r="S48" t="n">
+        <v>0</v>
+      </c>
+      <c r="T48" t="inlineStr"/>
+      <c r="U48" t="inlineStr">
         <is>
           <t>1. Heat shrimp in a non-stick pan with lime juice, paprika, and salt for 5 minutes.
 2. Serve over cooked corn.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U48" t="inlineStr"/>
-      <c r="V48" t="inlineStr">
+      <c r="V48" t="inlineStr"/>
+      <c r="W48" t="inlineStr">
         <is>
           <t>['Heat shrimp in a non-stick pan with lime juice, paprika, and salt for 5 minutes.', 'Serve over cooked corn.', 'Cook time: 5 MINS']</t>
         </is>
@@ -5080,10 +5320,15 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
+          <t>4537</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
           <t>['1 pound prawns, peeled and deveined', '1 teaspoon lemon juice', '2 cloves garlic, minced', '1 teaspoon dried oregano', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E49" t="inlineStr">
+      <c r="F49" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan.
 2. Toss prawns with lemon juice, garlic, oregano, and salt.
@@ -5091,59 +5336,59 @@
 4. Cook time: 3 MINS</t>
         </is>
       </c>
-      <c r="F49" t="inlineStr">
+      <c r="G49" t="inlineStr">
         <is>
           <t>{"calories": 280, "protein": 42, "carbs": 2, "fiber": 0, "fat": 2}</t>
         </is>
       </c>
-      <c r="G49" t="n">
+      <c r="H49" t="n">
         <v>4</v>
       </c>
-      <c r="H49" t="n">
+      <c r="I49" t="n">
         <v>15</v>
       </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J49" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K49" t="inlineStr">
+      <c r="L49" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
+      <c r="M49" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M49" t="inlineStr">
+      <c r="N49" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N49" t="b">
-        <v>0</v>
-      </c>
       <c r="O49" t="b">
         <v>0</v>
       </c>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="inlineStr">
+      <c r="P49" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q49" t="inlineStr"/>
+      <c r="R49" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R49" t="n">
-        <v>0</v>
-      </c>
-      <c r="S49" t="inlineStr"/>
-      <c r="T49" t="inlineStr">
+      <c r="S49" t="n">
+        <v>0</v>
+      </c>
+      <c r="T49" t="inlineStr"/>
+      <c r="U49" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan.
 2. Toss prawns with lemon juice, garlic, oregano, and salt.
@@ -5151,8 +5396,8 @@
 4. Cook time: 3 MINS</t>
         </is>
       </c>
-      <c r="U49" t="inlineStr"/>
-      <c r="V49" t="inlineStr">
+      <c r="V49" t="inlineStr"/>
+      <c r="W49" t="inlineStr">
         <is>
           <t>['Preheat grill or grill pan.', 'Toss prawns with lemon juice, garlic, oregano, and salt.', 'Grill for 3 minutes per side until opaque.', 'Cook time: 3 MINS']</t>
         </is>
@@ -5176,77 +5421,82 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
+          <t>4538</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
           <t>['1 pound cooked shrimp', '1 cup tomato juice', '1/2 cup diced cucumbers', '1/4 cup diced onions', '1 teaspoon lime juice', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E50" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>1. Mix shrimp, tomato juice, cucumbers, onions, lime juice, and salt in a bowl.
 2. Chill for 15 minutes before serving.
 3. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="F50" t="inlineStr">
+      <c r="G50" t="inlineStr">
         <is>
           <t>{"calories": 250, "protein": 38, "carbs": 12, "fiber": 3, "fat": 2}</t>
         </is>
       </c>
-      <c r="G50" t="n">
+      <c r="H50" t="n">
         <v>4</v>
       </c>
-      <c r="H50" t="n">
+      <c r="I50" t="n">
         <v>15</v>
       </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J50" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K50" t="inlineStr">
+      <c r="L50" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
+      <c r="M50" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M50" t="inlineStr">
+      <c r="N50" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N50" t="b">
-        <v>0</v>
-      </c>
       <c r="O50" t="b">
         <v>0</v>
       </c>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="inlineStr">
+      <c r="P50" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q50" t="inlineStr"/>
+      <c r="R50" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R50" t="n">
-        <v>0</v>
-      </c>
-      <c r="S50" t="inlineStr"/>
-      <c r="T50" t="inlineStr">
+      <c r="S50" t="n">
+        <v>0</v>
+      </c>
+      <c r="T50" t="inlineStr"/>
+      <c r="U50" t="inlineStr">
         <is>
           <t>1. Mix shrimp, tomato juice, cucumbers, onions, lime juice, and salt in a bowl.
 2. Chill for 15 minutes before serving.
 3. Cook time: 15 MINS</t>
         </is>
       </c>
-      <c r="U50" t="inlineStr"/>
-      <c r="V50" t="inlineStr">
+      <c r="V50" t="inlineStr"/>
+      <c r="W50" t="inlineStr">
         <is>
           <t>['Mix shrimp, tomato juice, cucumbers, onions, lime juice, and salt in a bowl.', 'Chill for 15 minutes before serving.', 'Cook time: 15 MINS']</t>
         </is>
@@ -5265,15 +5515,20 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Oil-Free Grilled Tuna Steaks with Garlic &amp; Lemon</t>
+          <t>Oil-Free Grilled Tuna Steaks With Garlic &amp; Lemon</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
+          <t>4539</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
           <t>['4 tuna steaks (low-mercury)', '1 teaspoon lemon juice', '2 cloves garlic, minced', '1 teaspoon dried basil', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E51" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan.
 2. Rub tuna steaks with lemon juice, garlic, basil, and salt.
@@ -5281,59 +5536,59 @@
 4. Cook time: 3 MINS</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>{"calories": 290, "protein": 45, "carbs": 2, "fiber": 0, "fat": 8}</t>
         </is>
       </c>
-      <c r="G51" t="n">
+      <c r="H51" t="n">
         <v>4</v>
       </c>
-      <c r="H51" t="n">
+      <c r="I51" t="n">
         <v>15</v>
       </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J51" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K51" t="inlineStr">
+      <c r="L51" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L51" t="inlineStr">
+      <c r="M51" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M51" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N51" t="b">
-        <v>0</v>
-      </c>
       <c r="O51" t="b">
         <v>0</v>
       </c>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="inlineStr">
+      <c r="P51" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q51" t="inlineStr"/>
+      <c r="R51" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R51" t="n">
-        <v>0</v>
-      </c>
-      <c r="S51" t="inlineStr"/>
-      <c r="T51" t="inlineStr">
+      <c r="S51" t="n">
+        <v>0</v>
+      </c>
+      <c r="T51" t="inlineStr"/>
+      <c r="U51" t="inlineStr">
         <is>
           <t>1. Preheat grill or grill pan.
 2. Rub tuna steaks with lemon juice, garlic, basil, and salt.
@@ -5341,8 +5596,8 @@
 4. Cook time: 3 MINS</t>
         </is>
       </c>
-      <c r="U51" t="inlineStr"/>
-      <c r="V51" t="inlineStr">
+      <c r="V51" t="inlineStr"/>
+      <c r="W51" t="inlineStr">
         <is>
           <t>['Preheat grill or grill pan.', 'Rub tuna steaks with lemon juice, garlic, basil, and salt.', 'Grill for 3 minutes per side.', 'Cook time: 3 MINS']</t>
         </is>
@@ -5366,77 +5621,82 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
+          <t>4540</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
           <t>['1 pound scallops', '1 teaspoon lemon juice', '2 cloves garlic, minced', '1 teaspoon dried oregano', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Cook scallops with lemon juice, garlic, oregano, and salt for 2 minutes per side.
 3. Cook time: 2 MINS</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="G52" t="inlineStr">
         <is>
           <t>{"calories": 250, "protein": 42, "carbs": 2, "fiber": 0, "fat": 1}</t>
         </is>
       </c>
-      <c r="G52" t="n">
+      <c r="H52" t="n">
         <v>4</v>
       </c>
-      <c r="H52" t="n">
+      <c r="I52" t="n">
         <v>10</v>
       </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J52" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="L52" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr">
+      <c r="M52" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M52" t="inlineStr">
+      <c r="N52" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N52" t="b">
-        <v>0</v>
-      </c>
       <c r="O52" t="b">
         <v>0</v>
       </c>
-      <c r="P52" t="inlineStr"/>
-      <c r="Q52" t="inlineStr">
+      <c r="P52" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q52" t="inlineStr"/>
+      <c r="R52" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R52" t="n">
-        <v>0</v>
-      </c>
-      <c r="S52" t="inlineStr"/>
-      <c r="T52" t="inlineStr">
+      <c r="S52" t="n">
+        <v>0</v>
+      </c>
+      <c r="T52" t="inlineStr"/>
+      <c r="U52" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Cook scallops with lemon juice, garlic, oregano, and salt for 2 minutes per side.
 3. Cook time: 2 MINS</t>
         </is>
       </c>
-      <c r="U52" t="inlineStr"/>
-      <c r="V52" t="inlineStr">
+      <c r="V52" t="inlineStr"/>
+      <c r="W52" t="inlineStr">
         <is>
           <t>['Heat a non-stick pan over medium heat.', 'Cook scallops with lemon juice, garlic, oregano, and salt for 2 minutes per side.', 'Cook time: 2 MINS']</t>
         </is>
@@ -5460,77 +5720,82 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
+          <t>4541</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
           <t>['2 pounds mussels, cleaned', '4 cups vegetable broth', '2 cloves garlic, minced', '1 teaspoon dried parsley', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>1. Bring broth, garlic, parsley, and salt to a boil.
 2. Add mussels, cover, and steam for 5 minutes until shells open.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>{"calories": 260, "protein": 42, "carbs": 10, "fiber": 2, "fat": 3}</t>
         </is>
       </c>
-      <c r="G53" t="n">
+      <c r="H53" t="n">
         <v>4</v>
       </c>
-      <c r="H53" t="n">
+      <c r="I53" t="n">
         <v>15</v>
       </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J53" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K53" t="inlineStr">
+      <c r="L53" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L53" t="inlineStr">
+      <c r="M53" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M53" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N53" t="b">
-        <v>0</v>
-      </c>
       <c r="O53" t="b">
         <v>0</v>
       </c>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="inlineStr">
+      <c r="P53" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q53" t="inlineStr"/>
+      <c r="R53" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R53" t="n">
-        <v>0</v>
-      </c>
-      <c r="S53" t="inlineStr"/>
-      <c r="T53" t="inlineStr">
+      <c r="S53" t="n">
+        <v>0</v>
+      </c>
+      <c r="T53" t="inlineStr"/>
+      <c r="U53" t="inlineStr">
         <is>
           <t>1. Bring broth, garlic, parsley, and salt to a boil.
 2. Add mussels, cover, and steam for 5 minutes until shells open.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr"/>
-      <c r="V53" t="inlineStr">
+      <c r="V53" t="inlineStr"/>
+      <c r="W53" t="inlineStr">
         <is>
           <t>['Bring broth, garlic, parsley, and salt to a boil.', 'Add mussels, cover, and steam for 5 minutes until shells open.', 'Cook time: 5 MINS']</t>
         </is>
@@ -5554,10 +5819,15 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
+          <t>4542</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
           <t>['4 tilapia fillets', '8 corn tortillas', '1 teaspoon chili powder', '1 teaspoon lime juice', '1/2 teaspoon salt', '1/2 cup shredded cabbage']</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="F54" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Cook tilapia with chili powder, lime juice, and salt for 5 minutes per side.
@@ -5565,59 +5835,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="G54" t="inlineStr">
         <is>
           <t>{"calories": 280, "protein": 40, "carbs": 35, "fiber": 6, "fat": 2}</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="H54" t="n">
         <v>4</v>
       </c>
-      <c r="H54" t="n">
+      <c r="I54" t="n">
         <v>15</v>
       </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J54" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K54" t="inlineStr">
+      <c r="L54" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M54" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N54" t="b">
-        <v>0</v>
-      </c>
       <c r="O54" t="b">
         <v>0</v>
       </c>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="inlineStr">
+      <c r="P54" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q54" t="inlineStr"/>
+      <c r="R54" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R54" t="n">
-        <v>0</v>
-      </c>
-      <c r="S54" t="inlineStr"/>
-      <c r="T54" t="inlineStr">
+      <c r="S54" t="n">
+        <v>0</v>
+      </c>
+      <c r="T54" t="inlineStr"/>
+      <c r="U54" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Cook tilapia with chili powder, lime juice, and salt for 5 minutes per side.
@@ -5625,8 +5895,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr"/>
-      <c r="V54" t="inlineStr">
+      <c r="V54" t="inlineStr"/>
+      <c r="W54" t="inlineStr">
         <is>
           <t>['Heat a non-stick pan over medium heat.', 'Cook tilapia with chili powder, lime juice, and salt for 5 minutes per side.', 'Serve in tortillas with shredded cabbage.', 'Cook time: 5 MINS']</t>
         </is>
@@ -5650,77 +5920,82 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
+          <t>4543</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
           <t>['2 pounds mussels, cleaned', '4 cups vegetable broth', '1 teaspoon dried parsley', '1 teaspoon lemon juice', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="F55" t="inlineStr">
         <is>
           <t>1. Bring broth, parsley, lemon juice, and salt to a boil.
 2. Add mussels, cover, and steam for 5 minutes.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F55" t="inlineStr">
+      <c r="G55" t="inlineStr">
         <is>
           <t>{"calories": 260, "protein": 42, "carbs": 10, "fiber": 2, "fat": 3}</t>
         </is>
       </c>
-      <c r="G55" t="n">
+      <c r="H55" t="n">
         <v>4</v>
       </c>
-      <c r="H55" t="n">
+      <c r="I55" t="n">
         <v>15</v>
       </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J55" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K55" t="inlineStr">
+      <c r="L55" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
+      <c r="M55" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M55" t="inlineStr">
+      <c r="N55" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N55" t="b">
-        <v>0</v>
-      </c>
       <c r="O55" t="b">
         <v>0</v>
       </c>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="inlineStr">
+      <c r="P55" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q55" t="inlineStr"/>
+      <c r="R55" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R55" t="n">
-        <v>0</v>
-      </c>
-      <c r="S55" t="inlineStr"/>
-      <c r="T55" t="inlineStr">
+      <c r="S55" t="n">
+        <v>0</v>
+      </c>
+      <c r="T55" t="inlineStr"/>
+      <c r="U55" t="inlineStr">
         <is>
           <t>1. Bring broth, parsley, lemon juice, and salt to a boil.
 2. Add mussels, cover, and steam for 5 minutes.
 3. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
-      <c r="V55" t="inlineStr">
+      <c r="V55" t="inlineStr"/>
+      <c r="W55" t="inlineStr">
         <is>
           <t>['Bring broth, parsley, lemon juice, and salt to a boil.', 'Add mussels, cover, and steam for 5 minutes.', 'Cook time: 5 MINS']</t>
         </is>
@@ -5744,10 +6019,15 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
+          <t>4544</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '1 teaspoon lime juice', '1 teaspoon Cajun seasoning', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E56" t="inlineStr">
+      <c r="F56" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Toss shrimp with lime juice, Cajun seasoning, and salt.
@@ -5755,59 +6035,59 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="F56" t="inlineStr">
+      <c r="G56" t="inlineStr">
         <is>
           <t>{"calories": 280, "protein": 38, "carbs": 3, "fiber": 1, "fat": 2}</t>
         </is>
       </c>
-      <c r="G56" t="n">
+      <c r="H56" t="n">
         <v>4</v>
       </c>
-      <c r="H56" t="n">
+      <c r="I56" t="n">
         <v>15</v>
       </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J56" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K56" t="inlineStr">
+      <c r="L56" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t>Savory</t>
-        </is>
-      </c>
       <c r="M56" t="inlineStr">
         <is>
+          <t>Spicy</t>
+        </is>
+      </c>
+      <c r="N56" t="inlineStr">
+        <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N56" t="b">
-        <v>0</v>
-      </c>
       <c r="O56" t="b">
         <v>0</v>
       </c>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="inlineStr">
+      <c r="P56" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q56" t="inlineStr"/>
+      <c r="R56" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R56" t="n">
-        <v>0</v>
-      </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr">
+      <c r="S56" t="n">
+        <v>0</v>
+      </c>
+      <c r="T56" t="inlineStr"/>
+      <c r="U56" t="inlineStr">
         <is>
           <t>1. Heat a non-stick pan over medium heat.
 2. Toss shrimp with lime juice, Cajun seasoning, and salt.
@@ -5815,8 +6095,8 @@
 4. Cook time: 5 MINS</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr"/>
-      <c r="V56" t="inlineStr">
+      <c r="V56" t="inlineStr"/>
+      <c r="W56" t="inlineStr">
         <is>
           <t>['Heat a non-stick pan over medium heat.', 'Toss shrimp with lime juice, Cajun seasoning, and salt.', 'Cook for 5 minutes, stirring occasionally.', 'Cook time: 5 MINS']</t>
         </is>
@@ -5840,77 +6120,82 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
+          <t>4545</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
           <t>['1 pound shrimp, peeled and deveined', '2 cups fish fillets (cod or tilapia), cut into chunks', '4 cups vegetable broth', '1 cup diced tomatoes', '1/2 teaspoon chili powder', '1/2 teaspoon salt']</t>
         </is>
       </c>
-      <c r="E57" t="inlineStr">
+      <c r="F57" t="inlineStr">
         <is>
           <t>1. Bring broth, tomatoes, chili powder, and salt to a boil.
 2. Add shrimp and fish chunks, then simmer for 10 minutes.
 3. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="F57" t="inlineStr">
+      <c r="G57" t="inlineStr">
         <is>
           <t>{"calories": 290, "protein": 42, "carbs": 10, "fiber": 2, "fat": 2}</t>
         </is>
       </c>
-      <c r="G57" t="n">
+      <c r="H57" t="n">
         <v>4</v>
       </c>
-      <c r="H57" t="n">
+      <c r="I57" t="n">
         <v>20</v>
       </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>['weight-loss', 'oil-free', 'whole-foods', 'lunches-and-dinners', 'seafood', 'soups', 'salads', 'bowls', 'tacos', 'wraps']</t>
-        </is>
-      </c>
       <c r="J57" t="inlineStr">
         <is>
+          <t>['animal-protein', 'lunches-and-dinners', 'oil-free', 'seafood', 'soups', 'weight-loss']</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
           <t>oil_free</t>
         </is>
       </c>
-      <c r="K57" t="inlineStr">
+      <c r="L57" t="inlineStr">
         <is>
           <t>whole_food</t>
         </is>
       </c>
-      <c r="L57" t="inlineStr">
+      <c r="M57" t="inlineStr">
         <is>
           <t>Savory</t>
         </is>
       </c>
-      <c r="M57" t="inlineStr">
+      <c r="N57" t="inlineStr">
         <is>
           <t>weight_loss</t>
         </is>
       </c>
-      <c r="N57" t="b">
-        <v>0</v>
-      </c>
       <c r="O57" t="b">
         <v>0</v>
       </c>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="inlineStr">
+      <c r="P57" t="b">
+        <v>0</v>
+      </c>
+      <c r="Q57" t="inlineStr"/>
+      <c r="R57" t="inlineStr">
         <is>
           <t>hot</t>
         </is>
       </c>
-      <c r="R57" t="n">
-        <v>0</v>
-      </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr">
+      <c r="S57" t="n">
+        <v>0</v>
+      </c>
+      <c r="T57" t="inlineStr"/>
+      <c r="U57" t="inlineStr">
         <is>
           <t>1. Bring broth, tomatoes, chili powder, and salt to a boil.
 2. Add shrimp and fish chunks, then simmer for 10 minutes.
 3. Cook time: 10 MINS</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
-      <c r="V57" t="inlineStr">
+      <c r="V57" t="inlineStr"/>
+      <c r="W57" t="inlineStr">
         <is>
           <t>['Bring broth, tomatoes, chili powder, and salt to a boil.', 'Add shrimp and fish chunks, then simmer for 10 minutes.', 'Cook time: 10 MINS']</t>
         </is>
